--- a/FON Macroeconomic Data.xlsx
+++ b/FON Macroeconomic Data.xlsx
@@ -6718,7 +6718,7 @@
         <v>2021</v>
       </c>
       <c r="B156" s="1" t="n">
-        <v>38221486</v>
+        <v>38224832.5</v>
       </c>
       <c r="C156" s="1" t="n">
         <v>527056</v>
@@ -6765,46 +6765,46 @@
         <v>2022</v>
       </c>
       <c r="B157" s="1" t="n">
-        <v>38865972.75</v>
+        <v>38873253</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>531308</v>
+        <v>531257</v>
       </c>
       <c r="D157" s="1" t="n">
-        <v>167213</v>
+        <v>167200</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>1025263</v>
+        <v>1024034</v>
       </c>
       <c r="F157" s="1" t="n">
-        <v>809264</v>
+        <v>808869</v>
       </c>
       <c r="G157" s="1" t="n">
-        <v>8673184</v>
+        <v>8669963</v>
       </c>
       <c r="H157" s="1" t="n">
-        <v>15141455</v>
+        <v>15155836</v>
       </c>
       <c r="I157" s="1" t="n">
-        <v>1412568</v>
+        <v>1413498</v>
       </c>
       <c r="J157" s="1" t="n">
-        <v>1178455</v>
+        <v>1178796</v>
       </c>
       <c r="K157" s="1" t="n">
-        <v>4510747</v>
+        <v>4512731</v>
       </c>
       <c r="L157" s="1" t="n">
-        <v>5357486</v>
+        <v>5358845</v>
       </c>
       <c r="M157" s="1" t="n">
-        <v>43900</v>
+        <v>43869</v>
       </c>
       <c r="N157" s="1" t="n">
-        <v>44634</v>
+        <v>44631</v>
       </c>
       <c r="O157" s="1" t="n">
-        <v>40457</v>
+        <v>40603</v>
       </c>
     </row>
     <row r="158">
@@ -6812,91 +6812,138 @@
         <v>2023</v>
       </c>
       <c r="B158" s="1" t="n">
-        <v>39968532.25</v>
+        <v>39936359</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>538907</v>
+        <v>538789</v>
       </c>
       <c r="D158" s="1" t="n">
-        <v>173713</v>
+        <v>173734</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>1056486</v>
+        <v>1053005</v>
       </c>
       <c r="F158" s="1" t="n">
-        <v>832190</v>
+        <v>831103</v>
       </c>
       <c r="G158" s="1" t="n">
-        <v>8848020</v>
+        <v>8821696</v>
       </c>
       <c r="H158" s="1" t="n">
-        <v>15623207</v>
+        <v>15632481</v>
       </c>
       <c r="I158" s="1" t="n">
-        <v>1454743</v>
+        <v>1453202</v>
       </c>
       <c r="J158" s="1" t="n">
-        <v>1209307</v>
+        <v>1210257</v>
       </c>
       <c r="K158" s="1" t="n">
-        <v>4684514</v>
+        <v>4688576</v>
       </c>
       <c r="L158" s="1" t="n">
-        <v>5531553</v>
+        <v>5515296</v>
       </c>
       <c r="M158" s="1" t="n">
-        <v>45463</v>
+        <v>45419</v>
       </c>
       <c r="N158" s="1" t="n">
-        <v>44681</v>
+        <v>44614</v>
       </c>
       <c r="O158" s="1" t="n">
-        <v>40700</v>
+        <v>40916</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
         <v>2024</v>
       </c>
-      <c r="B159" s="1"/>
+      <c r="B159" s="1" t="n">
+        <v>41117821</v>
+      </c>
       <c r="C159" s="1" t="n">
-        <v>545247</v>
+        <v>546869</v>
       </c>
       <c r="D159" s="1" t="n">
-        <v>178550</v>
+        <v>179709</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>1076374</v>
+        <v>1082769</v>
       </c>
       <c r="F159" s="1" t="n">
-        <v>854355</v>
+        <v>858293</v>
       </c>
       <c r="G159" s="1" t="n">
-        <v>9056044</v>
+        <v>8995474</v>
       </c>
       <c r="H159" s="1" t="n">
-        <v>16124116</v>
+        <v>16144797</v>
       </c>
       <c r="I159" s="1" t="n">
-        <v>1494301</v>
+        <v>1492144</v>
       </c>
       <c r="J159" s="1" t="n">
-        <v>1239865</v>
+        <v>1247868</v>
       </c>
       <c r="K159" s="1" t="n">
-        <v>4888723</v>
+        <v>4909030</v>
       </c>
       <c r="L159" s="1" t="n">
-        <v>5698430</v>
+        <v>5671114</v>
       </c>
       <c r="M159" s="1" t="n">
-        <v>46704</v>
+        <v>47595</v>
       </c>
       <c r="N159" s="1" t="n">
-        <v>44731</v>
+        <v>45257</v>
       </c>
       <c r="O159" s="1" t="n">
-        <v>41159</v>
+        <v>41410</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B160" s="1"/>
+      <c r="C160" s="1" t="n">
+        <v>549911</v>
+      </c>
+      <c r="D160" s="1" t="n">
+        <v>182657</v>
+      </c>
+      <c r="E160" s="1" t="n">
+        <v>1093245</v>
+      </c>
+      <c r="F160" s="1" t="n">
+        <v>869682</v>
+      </c>
+      <c r="G160" s="1" t="n">
+        <v>9058297</v>
+      </c>
+      <c r="H160" s="1" t="n">
+        <v>16258260</v>
+      </c>
+      <c r="I160" s="1" t="n">
+        <v>1509702</v>
+      </c>
+      <c r="J160" s="1" t="n">
+        <v>1266959</v>
+      </c>
+      <c r="K160" s="1" t="n">
+        <v>5029346</v>
+      </c>
+      <c r="L160" s="1" t="n">
+        <v>5697536</v>
+      </c>
+      <c r="M160" s="1" t="n">
+        <v>48278</v>
+      </c>
+      <c r="N160" s="1" t="n">
+        <v>45950</v>
+      </c>
+      <c r="O160" s="1" t="n">
+        <v>41830</v>
       </c>
     </row>
   </sheetData>
@@ -12189,20 +12236,61 @@
       <c r="A159" s="2" t="n">
         <v>2024</v>
       </c>
-      <c r="B159" s="4"/>
-      <c r="C159" s="4"/>
-      <c r="D159" s="4"/>
-      <c r="E159" s="4"/>
-      <c r="F159" s="4"/>
-      <c r="G159" s="4"/>
-      <c r="H159" s="4"/>
-      <c r="I159" s="4"/>
-      <c r="J159" s="4"/>
-      <c r="K159" s="4"/>
-      <c r="L159" s="4"/>
+      <c r="B159" s="4" t="n">
+        <v>117.445255474453</v>
+      </c>
+      <c r="C159" s="4" t="n">
+        <v>115.974212034384</v>
+      </c>
+      <c r="D159" s="4" t="n">
+        <v>119.869470630892</v>
+      </c>
+      <c r="E159" s="4" t="n">
+        <v>119.071791153009</v>
+      </c>
+      <c r="F159" s="4" t="n">
+        <v>117.862371888726</v>
+      </c>
+      <c r="G159" s="4" t="n">
+        <v>118.373493975904</v>
+      </c>
+      <c r="H159" s="4" t="n">
+        <v>117.413294797688</v>
+      </c>
+      <c r="I159" s="4" t="n">
+        <v>116.581818181818</v>
+      </c>
+      <c r="J159" s="4" t="n">
+        <v>115.351812366738</v>
+      </c>
+      <c r="K159" s="4" t="n">
+        <v>116.724257083621</v>
+      </c>
+      <c r="L159" s="4" t="n">
+        <v>117.220543806647</v>
+      </c>
       <c r="M159" s="4"/>
       <c r="N159" s="4"/>
       <c r="O159" s="4"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B160" s="4"/>
+      <c r="C160" s="4"/>
+      <c r="D160" s="4"/>
+      <c r="E160" s="4"/>
+      <c r="F160" s="4"/>
+      <c r="G160" s="4"/>
+      <c r="H160" s="4"/>
+      <c r="I160" s="4"/>
+      <c r="J160" s="4"/>
+      <c r="K160" s="4"/>
+      <c r="L160" s="4"/>
+      <c r="M160" s="4"/>
+      <c r="N160" s="4"/>
+      <c r="O160" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -17540,7 +17628,7 @@
         <v>2021</v>
       </c>
       <c r="B156" s="1" t="n">
-        <v>2517123</v>
+        <v>2535818</v>
       </c>
       <c r="C156" s="1" t="n">
         <v>38678</v>
@@ -17587,46 +17675,46 @@
         <v>2022</v>
       </c>
       <c r="B157" s="1" t="n">
-        <v>2813289</v>
+        <v>2850940</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>41209</v>
+        <v>42036</v>
       </c>
       <c r="D157" s="1" t="n">
-        <v>9461</v>
+        <v>9499</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>55173</v>
+        <v>56228</v>
       </c>
       <c r="F157" s="1" t="n">
-        <v>45571</v>
+        <v>44913</v>
       </c>
       <c r="G157" s="1" t="n">
-        <v>551681</v>
+        <v>556139</v>
       </c>
       <c r="H157" s="1" t="n">
-        <v>1061714</v>
+        <v>1065260</v>
       </c>
       <c r="I157" s="1" t="n">
-        <v>87881</v>
+        <v>88262</v>
       </c>
       <c r="J157" s="1" t="n">
-        <v>115195</v>
+        <v>117286</v>
       </c>
       <c r="K157" s="1" t="n">
-        <v>472776</v>
+        <v>469995</v>
       </c>
       <c r="L157" s="1" t="n">
-        <v>395629</v>
+        <v>400154</v>
       </c>
       <c r="M157" s="1" t="n">
-        <v>4072</v>
+        <v>3873</v>
       </c>
       <c r="N157" s="1" t="n">
-        <v>5505</v>
+        <v>5340</v>
       </c>
       <c r="O157" s="1" t="n">
-        <v>4320</v>
+        <v>4402</v>
       </c>
     </row>
     <row r="158">
@@ -17634,66 +17722,113 @@
         <v>2023</v>
       </c>
       <c r="B158" s="1" t="n">
-        <v>2892140</v>
+        <v>2933810</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>38959</v>
+        <v>40363</v>
       </c>
       <c r="D158" s="1" t="n">
-        <v>9924</v>
+        <v>10134</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>59574</v>
+        <v>60487</v>
       </c>
       <c r="F158" s="1" t="n">
-        <v>47035</v>
+        <v>46463</v>
       </c>
       <c r="G158" s="1" t="n">
-        <v>579460</v>
+        <v>582495</v>
       </c>
       <c r="H158" s="1" t="n">
-        <v>1119545</v>
+        <v>1138592</v>
       </c>
       <c r="I158" s="1" t="n">
-        <v>91872</v>
+        <v>93045</v>
       </c>
       <c r="J158" s="1" t="n">
-        <v>109702</v>
+        <v>112895</v>
       </c>
       <c r="K158" s="1" t="n">
-        <v>452410</v>
+        <v>451008</v>
       </c>
       <c r="L158" s="1" t="n">
-        <v>409881</v>
+        <v>414465</v>
       </c>
       <c r="M158" s="1" t="n">
-        <v>4330</v>
+        <v>4182</v>
       </c>
       <c r="N158" s="1" t="n">
-        <v>5478</v>
+        <v>5346</v>
       </c>
       <c r="O158" s="1" t="n">
-        <v>4825</v>
+        <v>4899</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
         <v>2024</v>
       </c>
-      <c r="B159" s="1"/>
-      <c r="C159" s="1"/>
-      <c r="D159" s="1"/>
-      <c r="E159" s="1"/>
-      <c r="F159" s="1"/>
-      <c r="G159" s="1"/>
-      <c r="H159" s="1"/>
-      <c r="I159" s="1"/>
-      <c r="J159" s="1"/>
-      <c r="K159" s="1"/>
-      <c r="L159" s="1"/>
-      <c r="M159" s="1"/>
-      <c r="N159" s="1"/>
-      <c r="O159" s="1"/>
+      <c r="B159" s="1" t="n">
+        <v>3072346</v>
+      </c>
+      <c r="C159" s="1" t="n">
+        <v>42219</v>
+      </c>
+      <c r="D159" s="1" t="n">
+        <v>10889</v>
+      </c>
+      <c r="E159" s="1" t="n">
+        <v>65338</v>
+      </c>
+      <c r="F159" s="1" t="n">
+        <v>48302</v>
+      </c>
+      <c r="G159" s="1" t="n">
+        <v>616771</v>
+      </c>
+      <c r="H159" s="1" t="n">
+        <v>1197020</v>
+      </c>
+      <c r="I159" s="1" t="n">
+        <v>96125</v>
+      </c>
+      <c r="J159" s="1" t="n">
+        <v>112839</v>
+      </c>
+      <c r="K159" s="1" t="n">
+        <v>473937</v>
+      </c>
+      <c r="L159" s="1" t="n">
+        <v>429089</v>
+      </c>
+      <c r="M159" s="1" t="n">
+        <v>4349</v>
+      </c>
+      <c r="N159" s="1" t="n">
+        <v>5123</v>
+      </c>
+      <c r="O159" s="1" t="n">
+        <v>5668</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B160" s="1"/>
+      <c r="C160" s="1"/>
+      <c r="D160" s="1"/>
+      <c r="E160" s="1"/>
+      <c r="F160" s="1"/>
+      <c r="G160" s="1"/>
+      <c r="H160" s="1"/>
+      <c r="I160" s="1"/>
+      <c r="J160" s="1"/>
+      <c r="K160" s="1"/>
+      <c r="L160" s="1"/>
+      <c r="M160" s="1"/>
+      <c r="N160" s="1"/>
+      <c r="O160" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -23031,7 +23166,7 @@
         <v>2021</v>
       </c>
       <c r="B156" s="1" t="n">
-        <v>2435352.05508475</v>
+        <v>2453439.73163842</v>
       </c>
       <c r="C156" s="1" t="n">
         <v>37421.511299435</v>
@@ -23078,46 +23213,46 @@
         <v>2022</v>
       </c>
       <c r="B157" s="1" t="n">
-        <v>2549077.99603175</v>
+        <v>2583192.98941799</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>37338.8425925926</v>
+        <v>38088.1746031746</v>
       </c>
       <c r="D157" s="1" t="n">
-        <v>8572.46693121693</v>
+        <v>8606.89814814815</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>49991.4087301587</v>
+        <v>50947.3280423281</v>
       </c>
       <c r="F157" s="1" t="n">
-        <v>41291.1838624339</v>
+        <v>40694.9801587302</v>
       </c>
       <c r="G157" s="1" t="n">
-        <v>499869.689153439</v>
+        <v>503909.014550265</v>
       </c>
       <c r="H157" s="1" t="n">
-        <v>962002.764550265</v>
+        <v>965215.740740741</v>
       </c>
       <c r="I157" s="1" t="n">
-        <v>79627.6256613757</v>
+        <v>79972.8439153439</v>
       </c>
       <c r="J157" s="1" t="n">
-        <v>104376.421957672</v>
+        <v>106271.044973545</v>
       </c>
       <c r="K157" s="1" t="n">
-        <v>428375.079365079</v>
+        <v>425855.257936508</v>
       </c>
       <c r="L157" s="1" t="n">
-        <v>358473.366402116</v>
+        <v>362573.3994709</v>
       </c>
       <c r="M157" s="1" t="n">
-        <v>3689.57671957672</v>
+        <v>3509.26587301587</v>
       </c>
       <c r="N157" s="1" t="n">
-        <v>4987.99603174603</v>
+        <v>4838.49206349206</v>
       </c>
       <c r="O157" s="1" t="n">
-        <v>3914.28571428572</v>
+        <v>3988.58465608466</v>
       </c>
     </row>
     <row r="158">
@@ -23125,66 +23260,113 @@
         <v>2023</v>
       </c>
       <c r="B158" s="1" t="n">
-        <v>2522108.08402292</v>
+        <v>2558446.6581795</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>33974.4302991725</v>
+        <v>35198.7969446213</v>
       </c>
       <c r="D158" s="1" t="n">
-        <v>8654.28389560789</v>
+        <v>8837.41565881604</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>51951.8650541057</v>
+        <v>52748.0521960535</v>
       </c>
       <c r="F158" s="1" t="n">
-        <v>41017.1546785487</v>
+        <v>40518.3386378103</v>
       </c>
       <c r="G158" s="1" t="n">
-        <v>505321.578612349</v>
+        <v>507968.268618714</v>
       </c>
       <c r="H158" s="1" t="n">
-        <v>976305.95162317</v>
+        <v>992916.002546149</v>
       </c>
       <c r="I158" s="1" t="n">
-        <v>80117.5302355188</v>
+        <v>81140.4519414386</v>
       </c>
       <c r="J158" s="1" t="n">
-        <v>95666.2889879058</v>
+        <v>98450.7638446849</v>
       </c>
       <c r="K158" s="1" t="n">
-        <v>394526.86187142</v>
+        <v>393304.239338001</v>
       </c>
       <c r="L158" s="1" t="n">
-        <v>357439.191597709</v>
+        <v>361436.696371738</v>
       </c>
       <c r="M158" s="1" t="n">
-        <v>3776.00254614895</v>
+        <v>3646.93825588797</v>
       </c>
       <c r="N158" s="1" t="n">
-        <v>4777.12285168682</v>
+        <v>4662.01145767027</v>
       </c>
       <c r="O158" s="1" t="n">
-        <v>4207.67027371101</v>
+        <v>4272.2024188415</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
         <v>2024</v>
       </c>
-      <c r="B159" s="1"/>
-      <c r="C159" s="1"/>
-      <c r="D159" s="1"/>
-      <c r="E159" s="1"/>
-      <c r="F159" s="1"/>
-      <c r="G159" s="1"/>
-      <c r="H159" s="1"/>
-      <c r="I159" s="1"/>
-      <c r="J159" s="1"/>
-      <c r="K159" s="1"/>
-      <c r="L159" s="1"/>
-      <c r="M159" s="1"/>
-      <c r="N159" s="1"/>
-      <c r="O159" s="1"/>
+      <c r="B159" s="1" t="n">
+        <v>2615981.36730889</v>
+      </c>
+      <c r="C159" s="1" t="n">
+        <v>35947.81230578</v>
+      </c>
+      <c r="D159" s="1" t="n">
+        <v>9271.55376009944</v>
+      </c>
+      <c r="E159" s="1" t="n">
+        <v>55632.7284027346</v>
+      </c>
+      <c r="F159" s="1" t="n">
+        <v>41127.2467371038</v>
+      </c>
+      <c r="G159" s="1" t="n">
+        <v>525156.165320075</v>
+      </c>
+      <c r="H159" s="1" t="n">
+        <v>1019215.28899938</v>
+      </c>
+      <c r="I159" s="1" t="n">
+        <v>81846.6438781852</v>
+      </c>
+      <c r="J159" s="1" t="n">
+        <v>96077.9552517091</v>
+      </c>
+      <c r="K159" s="1" t="n">
+        <v>403538.651336234</v>
+      </c>
+      <c r="L159" s="1" t="n">
+        <v>365352.34928527</v>
+      </c>
+      <c r="M159" s="1" t="n">
+        <v>3703.00186451212</v>
+      </c>
+      <c r="N159" s="1" t="n">
+        <v>4362.03231821007</v>
+      </c>
+      <c r="O159" s="1" t="n">
+        <v>4826.07830950901</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B160" s="1"/>
+      <c r="C160" s="1"/>
+      <c r="D160" s="1"/>
+      <c r="E160" s="1"/>
+      <c r="F160" s="1"/>
+      <c r="G160" s="1"/>
+      <c r="H160" s="1"/>
+      <c r="I160" s="1"/>
+      <c r="J160" s="1"/>
+      <c r="K160" s="1"/>
+      <c r="L160" s="1"/>
+      <c r="M160" s="1"/>
+      <c r="N160" s="1"/>
+      <c r="O160" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -28522,7 +28704,7 @@
         <v>2021</v>
       </c>
       <c r="B156" s="1" t="n">
-        <v>65856.2307075136</v>
+        <v>66339.5451111525</v>
       </c>
       <c r="C156" s="1" t="n">
         <v>73384.9913481679</v>
@@ -28569,46 +28751,46 @@
         <v>2022</v>
       </c>
       <c r="B157" s="1" t="n">
-        <v>72384.371236405</v>
+        <v>73339.3729616608</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>77561.4144714554</v>
+        <v>79125.5456398692</v>
       </c>
       <c r="D157" s="1" t="n">
-        <v>56580.5290258533</v>
+        <v>56812.2009569378</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>53813.5093141955</v>
+        <v>54908.3331217518</v>
       </c>
       <c r="F157" s="1" t="n">
-        <v>56311.6609660136</v>
+        <v>55525.6784473135</v>
       </c>
       <c r="G157" s="1" t="n">
-        <v>63607.6670343901</v>
+        <v>64145.4871260696</v>
       </c>
       <c r="H157" s="1" t="n">
-        <v>70119.6813648358</v>
+        <v>70287.1158014642</v>
       </c>
       <c r="I157" s="1" t="n">
-        <v>62213.6421043093</v>
+        <v>62442.2531903123</v>
       </c>
       <c r="J157" s="1" t="n">
-        <v>97750.8687221829</v>
+        <v>99496.4353458953</v>
       </c>
       <c r="K157" s="1" t="n">
-        <v>104811.021323076</v>
+        <v>104148.685131022</v>
       </c>
       <c r="L157" s="1" t="n">
-        <v>73846.0165831511</v>
+        <v>74671.687649111</v>
       </c>
       <c r="M157" s="1" t="n">
-        <v>92756.264236902</v>
+        <v>88285.5775148738</v>
       </c>
       <c r="N157" s="1" t="n">
-        <v>123336.469955639</v>
+        <v>119647.778449956</v>
       </c>
       <c r="O157" s="1" t="n">
-        <v>106780.038065106</v>
+        <v>108415.634312736</v>
       </c>
     </row>
     <row r="158">
@@ -28616,66 +28798,113 @@
         <v>2023</v>
       </c>
       <c r="B158" s="1" t="n">
-        <v>72360.4254944838</v>
+        <v>73462.1300855193</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>72292.6219180675</v>
+        <v>74914.2985472977</v>
       </c>
       <c r="D158" s="1" t="n">
-        <v>57128.7123013246</v>
+        <v>58330.551302566</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>56388.8210539468</v>
+        <v>57442.2723538825</v>
       </c>
       <c r="F158" s="1" t="n">
-        <v>56519.5448154868</v>
+        <v>55905.2247435035</v>
       </c>
       <c r="G158" s="1" t="n">
-        <v>65490.3582948501</v>
+        <v>66029.8201162225</v>
       </c>
       <c r="H158" s="1" t="n">
-        <v>71659.1030253904</v>
+        <v>72835.0157598145</v>
       </c>
       <c r="I158" s="1" t="n">
-        <v>63153.4229757421</v>
+        <v>64027.5749689307</v>
       </c>
       <c r="J158" s="1" t="n">
-        <v>90714.7647371594</v>
+        <v>93281.8401380864</v>
       </c>
       <c r="K158" s="1" t="n">
-        <v>96575.6533121686</v>
+        <v>96192.9592268527</v>
       </c>
       <c r="L158" s="1" t="n">
-        <v>74098.720558223</v>
+        <v>75148.2785330107</v>
       </c>
       <c r="M158" s="1" t="n">
-        <v>95242.2849350021</v>
+        <v>92076.0034346859</v>
       </c>
       <c r="N158" s="1" t="n">
-        <v>122602.448468029</v>
+        <v>119827.856726588</v>
       </c>
       <c r="O158" s="1" t="n">
-        <v>118550.368550369</v>
+        <v>119733.111741128</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
         <v>2024</v>
       </c>
-      <c r="B159" s="1"/>
-      <c r="C159" s="1"/>
-      <c r="D159" s="1"/>
-      <c r="E159" s="1"/>
-      <c r="F159" s="1"/>
-      <c r="G159" s="1"/>
-      <c r="H159" s="1"/>
-      <c r="I159" s="1"/>
-      <c r="J159" s="1"/>
-      <c r="K159" s="1"/>
-      <c r="L159" s="1"/>
-      <c r="M159" s="1"/>
-      <c r="N159" s="1"/>
-      <c r="O159" s="1"/>
+      <c r="B159" s="1" t="n">
+        <v>74720.5451378369</v>
+      </c>
+      <c r="C159" s="1" t="n">
+        <v>77201.3041514513</v>
+      </c>
+      <c r="D159" s="1" t="n">
+        <v>60592.4021612718</v>
+      </c>
+      <c r="E159" s="1" t="n">
+        <v>60343.4342874611</v>
+      </c>
+      <c r="F159" s="1" t="n">
+        <v>56276.8192214081</v>
+      </c>
+      <c r="G159" s="1" t="n">
+        <v>68564.5914823388</v>
+      </c>
+      <c r="H159" s="1" t="n">
+        <v>74142.7718168274</v>
+      </c>
+      <c r="I159" s="1" t="n">
+        <v>64420.726149755</v>
+      </c>
+      <c r="J159" s="1" t="n">
+        <v>90425.4296127475</v>
+      </c>
+      <c r="K159" s="1" t="n">
+        <v>96543.9200819714</v>
+      </c>
+      <c r="L159" s="1" t="n">
+        <v>75662.2067551455</v>
+      </c>
+      <c r="M159" s="1" t="n">
+        <v>91375.1444479462</v>
+      </c>
+      <c r="N159" s="1" t="n">
+        <v>113197.958326889</v>
+      </c>
+      <c r="O159" s="1" t="n">
+        <v>136875.150929727</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B160" s="1"/>
+      <c r="C160" s="1"/>
+      <c r="D160" s="1"/>
+      <c r="E160" s="1"/>
+      <c r="F160" s="1"/>
+      <c r="G160" s="1"/>
+      <c r="H160" s="1"/>
+      <c r="I160" s="1"/>
+      <c r="J160" s="1"/>
+      <c r="K160" s="1"/>
+      <c r="L160" s="1"/>
+      <c r="M160" s="1"/>
+      <c r="N160" s="1"/>
+      <c r="O160" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -34013,7 +34242,7 @@
         <v>2021</v>
       </c>
       <c r="B156" s="1" t="n">
-        <v>63716.8333822695</v>
+        <v>64184.4468942648</v>
       </c>
       <c r="C156" s="1" t="n">
         <v>71001.0156405297</v>
@@ -34060,46 +34289,46 @@
         <v>2022</v>
       </c>
       <c r="B157" s="1" t="n">
-        <v>65586.3681176421</v>
+        <v>66451.6805274308</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>70277.2075568081</v>
+        <v>71694.4428086117</v>
       </c>
       <c r="D157" s="1" t="n">
-        <v>51266.7491834782</v>
+        <v>51476.6635654794</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>48759.5950796613</v>
+        <v>49751.5981328042</v>
       </c>
       <c r="F157" s="1" t="n">
-        <v>51023.1319599462</v>
+        <v>50310.9652598012</v>
       </c>
       <c r="G157" s="1" t="n">
-        <v>57633.9311092027</v>
+        <v>58121.2416420075</v>
       </c>
       <c r="H157" s="1" t="n">
-        <v>63534.3673742229</v>
+        <v>63686.0771481521</v>
       </c>
       <c r="I157" s="1" t="n">
-        <v>56370.826509857</v>
+        <v>56577.9675070951</v>
       </c>
       <c r="J157" s="1" t="n">
-        <v>88570.5622681154</v>
+        <v>90152.1934020348</v>
       </c>
       <c r="K157" s="1" t="n">
-        <v>94967.6582094007</v>
+        <v>94367.5255486108</v>
       </c>
       <c r="L157" s="1" t="n">
-        <v>66910.7425389663</v>
+        <v>67658.8704228056</v>
       </c>
       <c r="M157" s="1" t="n">
-        <v>84045.0277807909</v>
+        <v>79994.2071397997</v>
       </c>
       <c r="N157" s="1" t="n">
-        <v>111753.282962451</v>
+        <v>108411.016188122</v>
       </c>
       <c r="O157" s="1" t="n">
-        <v>96751.7540669282</v>
+        <v>98233.7427304548</v>
       </c>
     </row>
     <row r="158">
@@ -34107,66 +34336,113 @@
         <v>2023</v>
       </c>
       <c r="B158" s="1" t="n">
-        <v>63102.3443204601</v>
+        <v>64063.0924361308</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>63043.215803789</v>
+        <v>65329.4646784201</v>
       </c>
       <c r="D158" s="1" t="n">
-        <v>49819.4372073932</v>
+        <v>50867.5081378201</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>49174.2105944666</v>
+        <v>50092.8791373768</v>
       </c>
       <c r="F158" s="1" t="n">
-        <v>49288.2090370573</v>
+        <v>48752.4875229789</v>
       </c>
       <c r="G158" s="1" t="n">
-        <v>57111.2608936631</v>
+        <v>57581.7018200031</v>
       </c>
       <c r="H158" s="1" t="n">
-        <v>62490.7518426383</v>
+        <v>63516.2136161336</v>
       </c>
       <c r="I158" s="1" t="n">
-        <v>55073.3223913219</v>
+        <v>55835.6318952483</v>
       </c>
       <c r="J158" s="1" t="n">
-        <v>79108.3562634681</v>
+        <v>81346.9898085158</v>
       </c>
       <c r="K158" s="1" t="n">
-        <v>84219.3794001725</v>
+        <v>83885.6487210619</v>
       </c>
       <c r="L158" s="1" t="n">
-        <v>64618.23498712</v>
+        <v>65533.5083324155</v>
       </c>
       <c r="M158" s="1" t="n">
-        <v>83056.6074862845</v>
+        <v>80295.4326578738</v>
       </c>
       <c r="N158" s="1" t="n">
-        <v>106916.20267422</v>
+        <v>104496.603256159</v>
       </c>
       <c r="O158" s="1" t="n">
-        <v>103382.562007642</v>
+        <v>104413.980321671</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
         <v>2024</v>
       </c>
-      <c r="B159" s="1"/>
-      <c r="C159" s="1"/>
-      <c r="D159" s="1"/>
-      <c r="E159" s="1"/>
-      <c r="F159" s="1"/>
-      <c r="G159" s="1"/>
-      <c r="H159" s="1"/>
-      <c r="I159" s="1"/>
-      <c r="J159" s="1"/>
-      <c r="K159" s="1"/>
-      <c r="L159" s="1"/>
-      <c r="M159" s="1"/>
-      <c r="N159" s="1"/>
-      <c r="O159" s="1"/>
+      <c r="B159" s="1" t="n">
+        <v>63621.5953007064</v>
+      </c>
+      <c r="C159" s="1" t="n">
+        <v>65733.863696388</v>
+      </c>
+      <c r="D159" s="1" t="n">
+        <v>51592.0391304801</v>
+      </c>
+      <c r="E159" s="1" t="n">
+        <v>51380.0528115735</v>
+      </c>
+      <c r="F159" s="1" t="n">
+        <v>47917.4905738527</v>
+      </c>
+      <c r="G159" s="1" t="n">
+        <v>58380.0437108789</v>
+      </c>
+      <c r="H159" s="1" t="n">
+        <v>63129.6441199836</v>
+      </c>
+      <c r="I159" s="1" t="n">
+        <v>54851.7059199281</v>
+      </c>
+      <c r="J159" s="1" t="n">
+        <v>76993.684629872</v>
+      </c>
+      <c r="K159" s="1" t="n">
+        <v>82203.3377950906</v>
+      </c>
+      <c r="L159" s="1" t="n">
+        <v>64423.3830046919</v>
+      </c>
+      <c r="M159" s="1" t="n">
+        <v>77802.3293310667</v>
+      </c>
+      <c r="N159" s="1" t="n">
+        <v>96383.5941005826</v>
+      </c>
+      <c r="O159" s="1" t="n">
+        <v>116543.7891695</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B160" s="1"/>
+      <c r="C160" s="1"/>
+      <c r="D160" s="1"/>
+      <c r="E160" s="1"/>
+      <c r="F160" s="1"/>
+      <c r="G160" s="1"/>
+      <c r="H160" s="1"/>
+      <c r="I160" s="1"/>
+      <c r="J160" s="1"/>
+      <c r="K160" s="1"/>
+      <c r="L160" s="1"/>
+      <c r="M160" s="1"/>
+      <c r="N160" s="1"/>
+      <c r="O160" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -38780,7 +39056,7 @@
         <v>110433.583181653</v>
       </c>
       <c r="M143" s="1" t="n">
-        <v>137749.286931769</v>
+        <v>137813.746120787</v>
       </c>
       <c r="N143" s="1" t="n">
         <v>270056.988820933</v>
@@ -38827,10 +39103,10 @@
         <v>107779.176432106</v>
       </c>
       <c r="M144" s="1" t="n">
-        <v>147715.415897234</v>
+        <v>147786.501275433</v>
       </c>
       <c r="N144" s="1" t="n">
-        <v>227412.090671759</v>
+        <v>227143.176098635</v>
       </c>
       <c r="O144" s="1" t="n">
         <v>169884.919077848</v>
@@ -38877,7 +39153,7 @@
         <v>157293.904587065</v>
       </c>
       <c r="N145" s="1" t="n">
-        <v>261746.320035829</v>
+        <v>261343.788209553</v>
       </c>
       <c r="O145" s="1" t="n">
         <v>195965.851973346</v>
@@ -38888,43 +39164,43 @@
         <v>2011</v>
       </c>
       <c r="B146" s="1" t="n">
-        <v>117550.600673033</v>
+        <v>117719.216659271</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>164798.340401846</v>
+        <v>164727.550736725</v>
       </c>
       <c r="D146" s="1" t="n">
-        <v>86084.6822190013</v>
+        <v>85965.4513572021</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>94772.8111522554</v>
+        <v>94544.1925288617</v>
       </c>
       <c r="F146" s="1" t="n">
-        <v>101042.850923449</v>
+        <v>101184.605764811</v>
       </c>
       <c r="G146" s="1" t="n">
-        <v>99397.5195866147</v>
+        <v>99580.410621797</v>
       </c>
       <c r="H146" s="1" t="n">
-        <v>113341.337065959</v>
+        <v>113518.656685895</v>
       </c>
       <c r="I146" s="1" t="n">
-        <v>104274.165308642</v>
+        <v>104426.637686835</v>
       </c>
       <c r="J146" s="1" t="n">
-        <v>158245.840081042</v>
+        <v>158128.815980409</v>
       </c>
       <c r="K146" s="1" t="n">
-        <v>162813.950290133</v>
+        <v>162976.679001575</v>
       </c>
       <c r="L146" s="1" t="n">
-        <v>111849.240781923</v>
+        <v>112110.090246903</v>
       </c>
       <c r="M146" s="1" t="n">
-        <v>149584.645125857</v>
+        <v>149323.475950605</v>
       </c>
       <c r="N146" s="1" t="n">
-        <v>239519.895115548</v>
+        <v>239431.543992304</v>
       </c>
       <c r="O146" s="1" t="n">
         <v>193999.052951817</v>
@@ -38935,46 +39211,46 @@
         <v>2012</v>
       </c>
       <c r="B147" s="1" t="n">
-        <v>117702.101672438</v>
+        <v>117999.199613739</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>150454.054568752</v>
+        <v>150391.365379348</v>
       </c>
       <c r="D147" s="1" t="n">
-        <v>86258.7960004193</v>
+        <v>86140.6332661722</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>93215.2327223463</v>
+        <v>93378.303324091</v>
       </c>
       <c r="F147" s="1" t="n">
-        <v>100829.539273438</v>
+        <v>101000.243911035</v>
       </c>
       <c r="G147" s="1" t="n">
-        <v>99635.0204776266</v>
+        <v>99968.7644218323</v>
       </c>
       <c r="H147" s="1" t="n">
-        <v>114335.489245368</v>
+        <v>114634.778900706</v>
       </c>
       <c r="I147" s="1" t="n">
-        <v>108437.195527019</v>
+        <v>108542.016402347</v>
       </c>
       <c r="J147" s="1" t="n">
-        <v>159775.900363482</v>
+        <v>159427.804719989</v>
       </c>
       <c r="K147" s="1" t="n">
-        <v>162475.863298796</v>
+        <v>162513.367537589</v>
       </c>
       <c r="L147" s="1" t="n">
-        <v>109515.842747578</v>
+        <v>110091.333250718</v>
       </c>
       <c r="M147" s="1" t="n">
-        <v>147230.804618144</v>
+        <v>147105.448462658</v>
       </c>
       <c r="N147" s="1" t="n">
-        <v>213898.776344134</v>
+        <v>214053.048811746</v>
       </c>
       <c r="O147" s="1" t="n">
-        <v>206956.692904375</v>
+        <v>207389.958835089</v>
       </c>
     </row>
     <row r="148">
@@ -38982,46 +39258,46 @@
         <v>2013</v>
       </c>
       <c r="B148" s="1" t="n">
-        <v>119816.492171409</v>
+        <v>120118.276438837</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>159071.405391358</v>
+        <v>159005.673405659</v>
       </c>
       <c r="D148" s="1" t="n">
-        <v>87164.6672492784</v>
+        <v>87046.717767209</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>94889.0233092545</v>
+        <v>95286.6614748645</v>
       </c>
       <c r="F148" s="1" t="n">
-        <v>99493.0690670339</v>
+        <v>99660.2843091634</v>
       </c>
       <c r="G148" s="1" t="n">
-        <v>100683.783535529</v>
+        <v>101045.255968248</v>
       </c>
       <c r="H148" s="1" t="n">
-        <v>114104.259889957</v>
+        <v>114373.100273152</v>
       </c>
       <c r="I148" s="1" t="n">
-        <v>111040.230195668</v>
+        <v>111164.376755542</v>
       </c>
       <c r="J148" s="1" t="n">
-        <v>164739.818317923</v>
+        <v>164099.147290348</v>
       </c>
       <c r="K148" s="1" t="n">
-        <v>172885.862962368</v>
+        <v>172581.458959861</v>
       </c>
       <c r="L148" s="1" t="n">
-        <v>110977.833469406</v>
+        <v>111796.325082846</v>
       </c>
       <c r="M148" s="1" t="n">
-        <v>153083.796577629</v>
+        <v>153149.780972706</v>
       </c>
       <c r="N148" s="1" t="n">
-        <v>214393.206142392</v>
+        <v>214011.043564598</v>
       </c>
       <c r="O148" s="1" t="n">
-        <v>206482.478722286</v>
+        <v>206067.02101862</v>
       </c>
     </row>
     <row r="149">
@@ -39029,46 +39305,46 @@
         <v>2014</v>
       </c>
       <c r="B149" s="1" t="n">
-        <v>122751.560075295</v>
+        <v>123060.886948219</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>156652.094545222</v>
+        <v>156456.197803398</v>
       </c>
       <c r="D149" s="1" t="n">
         <v>87450.3659084074</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>97305.1332154267</v>
+        <v>97544.6401443526</v>
       </c>
       <c r="F149" s="1" t="n">
-        <v>99333.102829656</v>
+        <v>99388.6893449496</v>
       </c>
       <c r="G149" s="1" t="n">
-        <v>102248.394733651</v>
+        <v>102581.575662712</v>
       </c>
       <c r="H149" s="1" t="n">
-        <v>116310.691198176</v>
+        <v>116593.652401373</v>
       </c>
       <c r="I149" s="1" t="n">
-        <v>111993.784638197</v>
+        <v>112011.612365774</v>
       </c>
       <c r="J149" s="1" t="n">
-        <v>160025.98347495</v>
+        <v>159575.60251882</v>
       </c>
       <c r="K149" s="1" t="n">
-        <v>183506.501751721</v>
+        <v>183229.240006196</v>
       </c>
       <c r="L149" s="1" t="n">
-        <v>113589.895379074</v>
+        <v>114516.04566539</v>
       </c>
       <c r="M149" s="1" t="n">
         <v>147428.141160722</v>
       </c>
       <c r="N149" s="1" t="n">
-        <v>229085.721146057</v>
+        <v>228668.594924014</v>
       </c>
       <c r="O149" s="1" t="n">
-        <v>216099.103313152</v>
+        <v>215355.472537814</v>
       </c>
     </row>
     <row r="150">
@@ -39076,46 +39352,46 @@
         <v>2015</v>
       </c>
       <c r="B150" s="1" t="n">
-        <v>120292.905741475</v>
+        <v>120620.967504215</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>140738.019131412</v>
+        <v>140444.937042425</v>
       </c>
       <c r="D150" s="1" t="n">
-        <v>90372.017327725</v>
+        <v>90620.6336064808</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>99132.401679835</v>
+        <v>99266.4549613494</v>
       </c>
       <c r="F150" s="1" t="n">
-        <v>102032.451364363</v>
+        <v>102061.217209123</v>
       </c>
       <c r="G150" s="1" t="n">
-        <v>103578.406558512</v>
+        <v>103791.10374905</v>
       </c>
       <c r="H150" s="1" t="n">
-        <v>119486.509945817</v>
+        <v>119909.597388322</v>
       </c>
       <c r="I150" s="1" t="n">
-        <v>111955.002327286</v>
+        <v>111867.249542894</v>
       </c>
       <c r="J150" s="1" t="n">
-        <v>152557.665281425</v>
+        <v>152476.732833</v>
       </c>
       <c r="K150" s="1" t="n">
-        <v>154782.198871395</v>
+        <v>154960.030827677</v>
       </c>
       <c r="L150" s="1" t="n">
-        <v>113602.716407513</v>
+        <v>114267.591253014</v>
       </c>
       <c r="M150" s="1" t="n">
-        <v>140866.342909524</v>
+        <v>140924.336463624</v>
       </c>
       <c r="N150" s="1" t="n">
-        <v>221961.899990048</v>
+        <v>221240.98440004</v>
       </c>
       <c r="O150" s="1" t="n">
-        <v>215924.300817666</v>
+        <v>214597.803406499</v>
       </c>
     </row>
     <row r="151">
@@ -39123,46 +39399,46 @@
         <v>2016</v>
       </c>
       <c r="B151" s="1" t="n">
-        <v>120008.755460129</v>
+        <v>120287.955877465</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>143411.879188836</v>
+        <v>143045.876945053</v>
       </c>
       <c r="D151" s="1" t="n">
-        <v>93835.2132345042</v>
+        <v>94355.7969417692</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>100147.170254282</v>
+        <v>100441.787410495</v>
       </c>
       <c r="F151" s="1" t="n">
         <v>102431.100029968</v>
       </c>
       <c r="G151" s="1" t="n">
-        <v>104574.75981609</v>
+        <v>104824.384574977</v>
       </c>
       <c r="H151" s="1" t="n">
-        <v>121285.713767514</v>
+        <v>121668.748900762</v>
       </c>
       <c r="I151" s="1" t="n">
-        <v>112618.410355031</v>
+        <v>112547.803201203</v>
       </c>
       <c r="J151" s="1" t="n">
         <v>143938.419804001</v>
       </c>
       <c r="K151" s="1" t="n">
-        <v>147271.64215971</v>
+        <v>147693.700725695</v>
       </c>
       <c r="L151" s="1" t="n">
-        <v>114100.388552882</v>
+        <v>114248.528790383</v>
       </c>
       <c r="M151" s="1" t="n">
-        <v>141704.865746922</v>
+        <v>141873.763083926</v>
       </c>
       <c r="N151" s="1" t="n">
-        <v>203706.240665065</v>
+        <v>203633.436433233</v>
       </c>
       <c r="O151" s="1" t="n">
-        <v>213423.19132633</v>
+        <v>212326.604601468</v>
       </c>
     </row>
     <row r="152">
@@ -39170,46 +39446,46 @@
         <v>2017</v>
       </c>
       <c r="B152" s="1" t="n">
-        <v>122260.740782121</v>
+        <v>122412.467025567</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>156823.964163298</v>
+        <v>156063.354107833</v>
       </c>
       <c r="D152" s="1" t="n">
-        <v>95115.5419222904</v>
+        <v>96141.0464174094</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>101780.972950425</v>
+        <v>102307.268449044</v>
       </c>
       <c r="F152" s="1" t="n">
-        <v>104530.353702022</v>
+        <v>104733.946488865</v>
       </c>
       <c r="G152" s="1" t="n">
-        <v>105288.688803582</v>
+        <v>105607.20155932</v>
       </c>
       <c r="H152" s="1" t="n">
-        <v>121778.493541918</v>
+        <v>121917.244146443</v>
       </c>
       <c r="I152" s="1" t="n">
-        <v>115557.758260815</v>
+        <v>115433.081271323</v>
       </c>
       <c r="J152" s="1" t="n">
         <v>149900.599863667</v>
       </c>
       <c r="K152" s="1" t="n">
-        <v>157162.053953811</v>
+        <v>157353.334852511</v>
       </c>
       <c r="L152" s="1" t="n">
-        <v>115834.21073882</v>
+        <v>115716.699736471</v>
       </c>
       <c r="M152" s="1" t="n">
-        <v>136437.779804344</v>
+        <v>136489.014419366</v>
       </c>
       <c r="N152" s="1" t="n">
-        <v>215653.47062359</v>
+        <v>216212.986670426</v>
       </c>
       <c r="O152" s="1" t="n">
-        <v>247974.783325305</v>
+        <v>245426.551768975</v>
       </c>
     </row>
     <row r="153">
@@ -39217,46 +39493,46 @@
         <v>2018</v>
       </c>
       <c r="B153" s="1" t="n">
-        <v>122628.385940019</v>
+        <v>122737.860352537</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>156693.587480631</v>
+        <v>155800.159130961</v>
       </c>
       <c r="D153" s="1" t="n">
-        <v>93135.6724235285</v>
+        <v>94237.1455533731</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>102005.355224114</v>
+        <v>102163.643294735</v>
       </c>
       <c r="F153" s="1" t="n">
-        <v>105591.490364392</v>
+        <v>106031.577153907</v>
       </c>
       <c r="G153" s="1" t="n">
-        <v>106164.757298778</v>
+        <v>106417.459044799</v>
       </c>
       <c r="H153" s="1" t="n">
-        <v>121905.519314205</v>
+        <v>121998.121982045</v>
       </c>
       <c r="I153" s="1" t="n">
-        <v>115217.207909807</v>
+        <v>115287.720276948</v>
       </c>
       <c r="J153" s="1" t="n">
-        <v>151685.816403361</v>
+        <v>152034.704516107</v>
       </c>
       <c r="K153" s="1" t="n">
-        <v>155914.937579673</v>
+        <v>155969.661376481</v>
       </c>
       <c r="L153" s="1" t="n">
-        <v>117179.853903619</v>
+        <v>117022.710147666</v>
       </c>
       <c r="M153" s="1" t="n">
-        <v>137324.078094981</v>
+        <v>137119.878722349</v>
       </c>
       <c r="N153" s="1" t="n">
-        <v>213389.590603742</v>
+        <v>215770.28518095</v>
       </c>
       <c r="O153" s="1" t="n">
-        <v>250268.711797947</v>
+        <v>248200.375336807</v>
       </c>
     </row>
     <row r="154">
@@ -39264,46 +39540,46 @@
         <v>2019</v>
       </c>
       <c r="B154" s="1" t="n">
-        <v>121884.321729131</v>
+        <v>122206.435631807</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>156948.129621575</v>
+        <v>155998.162559447</v>
       </c>
       <c r="D154" s="1" t="n">
-        <v>94273.0299667037</v>
+        <v>95962.9434360172</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>101546.206730647</v>
+        <v>101721.36189534</v>
       </c>
       <c r="F154" s="1" t="n">
-        <v>105436.828609332</v>
+        <v>105990.685325831</v>
       </c>
       <c r="G154" s="1" t="n">
-        <v>106956.612095042</v>
+        <v>107712.717717369</v>
       </c>
       <c r="H154" s="1" t="n">
-        <v>121115.5741573</v>
+        <v>121381.89150392</v>
       </c>
       <c r="I154" s="1" t="n">
-        <v>113659.994841602</v>
+        <v>113625.635713778</v>
       </c>
       <c r="J154" s="1" t="n">
-        <v>147551.275580435</v>
+        <v>148167.677776071</v>
       </c>
       <c r="K154" s="1" t="n">
-        <v>153696.183148708</v>
+        <v>153849.512674295</v>
       </c>
       <c r="L154" s="1" t="n">
-        <v>116243.420604601</v>
+        <v>116096.008113439</v>
       </c>
       <c r="M154" s="1" t="n">
-        <v>133753.279729158</v>
+        <v>133609.097250111</v>
       </c>
       <c r="N154" s="1" t="n">
-        <v>203284.331377492</v>
+        <v>206481.561168725</v>
       </c>
       <c r="O154" s="1" t="n">
-        <v>269094.62915601</v>
+        <v>267764.124191086</v>
       </c>
     </row>
     <row r="155">
@@ -39311,46 +39587,46 @@
         <v>2020</v>
       </c>
       <c r="B155" s="1" t="n">
-        <v>123063.157428036</v>
+        <v>122894.927636494</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>149308.584686775</v>
+        <v>148071.790151864</v>
       </c>
       <c r="D155" s="1" t="n">
-        <v>97148.4375</v>
+        <v>97913.3858267717</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>104139.408978119</v>
+        <v>103231.216457961</v>
       </c>
       <c r="F155" s="1" t="n">
-        <v>105998.86492622</v>
+        <v>106270.27027027</v>
       </c>
       <c r="G155" s="1" t="n">
-        <v>110169.888693615</v>
+        <v>110420.550458716</v>
       </c>
       <c r="H155" s="1" t="n">
-        <v>124447.259425839</v>
+        <v>124138.058324105</v>
       </c>
       <c r="I155" s="1" t="n">
-        <v>115338.286436927</v>
+        <v>114793.895531781</v>
       </c>
       <c r="J155" s="1" t="n">
-        <v>142060.273972603</v>
+        <v>142633.412800293</v>
       </c>
       <c r="K155" s="1" t="n">
-        <v>140553.715538555</v>
+        <v>140987.787188246</v>
       </c>
       <c r="L155" s="1" t="n">
-        <v>122513.948668898</v>
+        <v>121636.529102204</v>
       </c>
       <c r="M155" s="1" t="n">
-        <v>147643.263757116</v>
+        <v>145762.457849382</v>
       </c>
       <c r="N155" s="1" t="n">
-        <v>191972.529568867</v>
+        <v>194947.69469198</v>
       </c>
       <c r="O155" s="1" t="n">
-        <v>328787.061994609</v>
+        <v>327683.008730692</v>
       </c>
     </row>
     <row r="156">
@@ -39358,46 +39634,46 @@
         <v>2021</v>
       </c>
       <c r="B156" s="1" t="n">
-        <v>128566.861209291</v>
+        <v>129372.853530535</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>167960.104575561</v>
+        <v>166243.941801133</v>
       </c>
       <c r="D156" s="1" t="n">
-        <v>103738.341712451</v>
+        <v>103608.668785311</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>106207.462672156</v>
+        <v>104554.602054335</v>
       </c>
       <c r="F156" s="1" t="n">
-        <v>109900.0225367</v>
+        <v>109568.453626139</v>
       </c>
       <c r="G156" s="1" t="n">
-        <v>114891.792851271</v>
+        <v>115204.511607917</v>
       </c>
       <c r="H156" s="1" t="n">
-        <v>126956.833569194</v>
+        <v>126759.663681277</v>
       </c>
       <c r="I156" s="1" t="n">
-        <v>116893.458226357</v>
+        <v>115520.312180927</v>
       </c>
       <c r="J156" s="1" t="n">
-        <v>152184.098112168</v>
+        <v>153110.886458185</v>
       </c>
       <c r="K156" s="1" t="n">
-        <v>162730.857443895</v>
+        <v>163723.516398872</v>
       </c>
       <c r="L156" s="1" t="n">
-        <v>129661.202523041</v>
+        <v>128694.987667622</v>
       </c>
       <c r="M156" s="1" t="n">
-        <v>156974.670783189</v>
+        <v>154053.945423852</v>
       </c>
       <c r="N156" s="1" t="n">
-        <v>198172.868043495</v>
+        <v>200607.952074388</v>
       </c>
       <c r="O156" s="1" t="n">
-        <v>315653.71577575</v>
+        <v>315072.044309332</v>
       </c>
     </row>
     <row r="157">
@@ -39405,46 +39681,46 @@
         <v>2022</v>
       </c>
       <c r="B157" s="1" t="n">
-        <v>129440.816332288</v>
+        <v>130864.155090959</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>160597.172441258</v>
+        <v>162630.976102368</v>
       </c>
       <c r="D157" s="1" t="n">
-        <v>101810.771154595</v>
+        <v>102341.238384639</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>103096.32652126</v>
+        <v>103530.436989084</v>
       </c>
       <c r="F157" s="1" t="n">
-        <v>110552.031760198</v>
+        <v>108346.59254188</v>
       </c>
       <c r="G157" s="1" t="n">
-        <v>113526.762770194</v>
+        <v>114733.382183576</v>
       </c>
       <c r="H157" s="1" t="n">
-        <v>124424.797525773</v>
+        <v>124317.78837737</v>
       </c>
       <c r="I157" s="1" t="n">
-        <v>117531.550791698</v>
+        <v>116256.496460741</v>
       </c>
       <c r="J157" s="1" t="n">
-        <v>179495.1366426</v>
+        <v>183923.580778029</v>
       </c>
       <c r="K157" s="1" t="n">
-        <v>180284.954069727</v>
+        <v>180753.50506643</v>
       </c>
       <c r="L157" s="1" t="n">
-        <v>130453.570509158</v>
+        <v>130624.130659257</v>
       </c>
       <c r="M157" s="1" t="n">
-        <v>158464.282873732</v>
+        <v>147139.030315131</v>
       </c>
       <c r="N157" s="1" t="n">
-        <v>201670.998588114</v>
+        <v>197691.197691198</v>
       </c>
       <c r="O157" s="1" t="n">
-        <v>271982.794275788</v>
+        <v>279084.640658985</v>
       </c>
     </row>
     <row r="158">
@@ -39452,66 +39728,113 @@
         <v>2023</v>
       </c>
       <c r="B158" s="1" t="n">
-        <v>125036.963349326</v>
+        <v>125816.170219501</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>143533.714825401</v>
+        <v>147707.918357622</v>
       </c>
       <c r="D158" s="1" t="n">
-        <v>97239.1448944707</v>
+        <v>98963.2212633375</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>104362.926986954</v>
+        <v>104389.574898186</v>
       </c>
       <c r="F158" s="1" t="n">
-        <v>106124.591665068</v>
+        <v>104267.46947455</v>
       </c>
       <c r="G158" s="1" t="n">
-        <v>112134.204378739</v>
+        <v>112312.786021649</v>
       </c>
       <c r="H158" s="1" t="n">
-        <v>123351.942136652</v>
+        <v>124019.935117741</v>
       </c>
       <c r="I158" s="1" t="n">
-        <v>115343.406616065</v>
+        <v>114799.733929596</v>
       </c>
       <c r="J158" s="1" t="n">
-        <v>161543.885491229</v>
+        <v>167718.507401508</v>
       </c>
       <c r="K158" s="1" t="n">
-        <v>160305.091979773</v>
+        <v>161018.684736756</v>
       </c>
       <c r="L158" s="1" t="n">
-        <v>128031.80442643</v>
+        <v>126913.408606952</v>
       </c>
       <c r="M158" s="1" t="n">
-        <v>158378.296238334</v>
+        <v>147004.565235659</v>
       </c>
       <c r="N158" s="1" t="n">
-        <v>200860.105887323</v>
+        <v>197194.703884538</v>
       </c>
       <c r="O158" s="1" t="n">
-        <v>296314.808007818</v>
+        <v>305157.315631536</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
         <v>2024</v>
       </c>
-      <c r="B159" s="1"/>
-      <c r="C159" s="1"/>
-      <c r="D159" s="1"/>
-      <c r="E159" s="1"/>
-      <c r="F159" s="1"/>
-      <c r="G159" s="1"/>
-      <c r="H159" s="1"/>
-      <c r="I159" s="1"/>
-      <c r="J159" s="1"/>
-      <c r="K159" s="1"/>
-      <c r="L159" s="1"/>
-      <c r="M159" s="1"/>
-      <c r="N159" s="1"/>
-      <c r="O159" s="1"/>
+      <c r="B159" s="1" t="n">
+        <v>126189.979368992</v>
+      </c>
+      <c r="C159" s="1" t="n">
+        <v>146725.764513388</v>
+      </c>
+      <c r="D159" s="1" t="n">
+        <v>100233.013622697</v>
+      </c>
+      <c r="E159" s="1" t="n">
+        <v>106719.218113821</v>
+      </c>
+      <c r="F159" s="1" t="n">
+        <v>102818.116842759</v>
+      </c>
+      <c r="G159" s="1" t="n">
+        <v>115014.490871676</v>
+      </c>
+      <c r="H159" s="1" t="n">
+        <v>125116.962595522</v>
+      </c>
+      <c r="I159" s="1" t="n">
+        <v>112985.427772205</v>
+      </c>
+      <c r="J159" s="1" t="n">
+        <v>159544.927352556</v>
+      </c>
+      <c r="K159" s="1" t="n">
+        <v>160204.315906242</v>
+      </c>
+      <c r="L159" s="1" t="n">
+        <v>125378.294195357</v>
+      </c>
+      <c r="M159" s="1" t="n">
+        <v>140353.829356113</v>
+      </c>
+      <c r="N159" s="1" t="n">
+        <v>190204.897596369</v>
+      </c>
+      <c r="O159" s="1" t="n">
+        <v>337487.993671959</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B160" s="1"/>
+      <c r="C160" s="1"/>
+      <c r="D160" s="1"/>
+      <c r="E160" s="1"/>
+      <c r="F160" s="1"/>
+      <c r="G160" s="1"/>
+      <c r="H160" s="1"/>
+      <c r="I160" s="1"/>
+      <c r="J160" s="1"/>
+      <c r="K160" s="1"/>
+      <c r="L160" s="1"/>
+      <c r="M160" s="1"/>
+      <c r="N160" s="1"/>
+      <c r="O160" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -44215,7 +44538,7 @@
         <v>2244400</v>
       </c>
       <c r="M143" s="1" t="n">
-        <v>17816.6666666667</v>
+        <v>17808.3333333333</v>
       </c>
       <c r="N143" s="1" t="n">
         <v>22341.6666666667</v>
@@ -44262,10 +44585,10 @@
         <v>2202000</v>
       </c>
       <c r="M144" s="1" t="n">
-        <v>17325</v>
+        <v>17316.6666666667</v>
       </c>
       <c r="N144" s="1" t="n">
-        <v>21116.6666666667</v>
+        <v>21141.6666666667</v>
       </c>
       <c r="O144" s="1" t="n">
         <v>10841.6666666667</v>
@@ -44312,7 +44635,7 @@
         <v>17300</v>
       </c>
       <c r="N145" s="1" t="n">
-        <v>21641.6666666667</v>
+        <v>21675</v>
       </c>
       <c r="O145" s="1" t="n">
         <v>11491.6666666667</v>
@@ -44323,43 +44646,43 @@
         <v>2011</v>
       </c>
       <c r="B146" s="1" t="n">
-        <v>17244300</v>
+        <v>17219600</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>232700</v>
+        <v>232800</v>
       </c>
       <c r="D146" s="1" t="n">
-        <v>72100</v>
+        <v>72200</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>454900</v>
+        <v>456000</v>
       </c>
       <c r="F146" s="1" t="n">
-        <v>356900</v>
+        <v>356400</v>
       </c>
       <c r="G146" s="1" t="n">
-        <v>3974700</v>
+        <v>3967400</v>
       </c>
       <c r="H146" s="1" t="n">
-        <v>6658000</v>
+        <v>6647600</v>
       </c>
       <c r="I146" s="1" t="n">
-        <v>616400</v>
+        <v>615500</v>
       </c>
       <c r="J146" s="1" t="n">
-        <v>540500</v>
+        <v>540900</v>
       </c>
       <c r="K146" s="1" t="n">
-        <v>2103200</v>
+        <v>2101100</v>
       </c>
       <c r="L146" s="1" t="n">
-        <v>2234900</v>
+        <v>2229700</v>
       </c>
       <c r="M146" s="1" t="n">
-        <v>19058.3333333333</v>
+        <v>19091.6666666667</v>
       </c>
       <c r="N146" s="1" t="n">
-        <v>22583.3333333333</v>
+        <v>22591.6666666667</v>
       </c>
       <c r="O146" s="1" t="n">
         <v>11991.6666666667</v>
@@ -44370,46 +44693,46 @@
         <v>2012</v>
       </c>
       <c r="B147" s="1" t="n">
-        <v>17475600</v>
+        <v>17431600</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>239900</v>
+        <v>240000</v>
       </c>
       <c r="D147" s="1" t="n">
-        <v>72900</v>
+        <v>73000</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>458100</v>
+        <v>457300</v>
       </c>
       <c r="F147" s="1" t="n">
-        <v>355000</v>
+        <v>354400</v>
       </c>
       <c r="G147" s="1" t="n">
-        <v>4013800</v>
+        <v>4000400</v>
       </c>
       <c r="H147" s="1" t="n">
-        <v>6702900</v>
+        <v>6685400</v>
       </c>
       <c r="I147" s="1" t="n">
-        <v>621300</v>
+        <v>620700</v>
       </c>
       <c r="J147" s="1" t="n">
-        <v>549600</v>
+        <v>550800</v>
       </c>
       <c r="K147" s="1" t="n">
-        <v>2166600</v>
+        <v>2166100</v>
       </c>
       <c r="L147" s="1" t="n">
-        <v>2295600</v>
+        <v>2283600</v>
       </c>
       <c r="M147" s="1" t="n">
-        <v>19558.3333333333</v>
+        <v>19575</v>
       </c>
       <c r="N147" s="1" t="n">
-        <v>23125</v>
+        <v>23108.3333333333</v>
       </c>
       <c r="O147" s="1" t="n">
-        <v>11966.6666666667</v>
+        <v>11941.6666666667</v>
       </c>
     </row>
     <row r="148">
@@ -44417,46 +44740,46 @@
         <v>2013</v>
       </c>
       <c r="B148" s="1" t="n">
-        <v>17712200</v>
+        <v>17667700</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>241900</v>
+        <v>242000</v>
       </c>
       <c r="D148" s="1" t="n">
-        <v>73800</v>
+        <v>73900</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>455300</v>
+        <v>453400</v>
       </c>
       <c r="F148" s="1" t="n">
-        <v>357600</v>
+        <v>357000</v>
       </c>
       <c r="G148" s="1" t="n">
-        <v>4053300</v>
+        <v>4038800</v>
       </c>
       <c r="H148" s="1" t="n">
-        <v>6806900</v>
+        <v>6790900</v>
       </c>
       <c r="I148" s="1" t="n">
-        <v>626800</v>
+        <v>626100</v>
       </c>
       <c r="J148" s="1" t="n">
-        <v>563500</v>
+        <v>565700</v>
       </c>
       <c r="K148" s="1" t="n">
-        <v>2211100</v>
+        <v>2215000</v>
       </c>
       <c r="L148" s="1" t="n">
-        <v>2322000</v>
+        <v>2305000</v>
       </c>
       <c r="M148" s="1" t="n">
-        <v>19341.6666666667</v>
+        <v>19333.3333333333</v>
       </c>
       <c r="N148" s="1" t="n">
-        <v>23333.3333333333</v>
+        <v>23375</v>
       </c>
       <c r="O148" s="1" t="n">
-        <v>12400</v>
+        <v>12425</v>
       </c>
     </row>
     <row r="149">
@@ -44464,46 +44787,46 @@
         <v>2014</v>
       </c>
       <c r="B149" s="1" t="n">
-        <v>17783200</v>
+        <v>17738500</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>239600</v>
+        <v>239900</v>
       </c>
       <c r="D149" s="1" t="n">
         <v>73300</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>448000</v>
+        <v>446900</v>
       </c>
       <c r="F149" s="1" t="n">
-        <v>357600</v>
+        <v>357400</v>
       </c>
       <c r="G149" s="1" t="n">
-        <v>4033300</v>
+        <v>4020200</v>
       </c>
       <c r="H149" s="1" t="n">
-        <v>6840000</v>
+        <v>6823400</v>
       </c>
       <c r="I149" s="1" t="n">
-        <v>628300</v>
+        <v>628200</v>
       </c>
       <c r="J149" s="1" t="n">
-        <v>566900</v>
+        <v>568500</v>
       </c>
       <c r="K149" s="1" t="n">
-        <v>2246900</v>
+        <v>2250300</v>
       </c>
       <c r="L149" s="1" t="n">
-        <v>2349300</v>
+        <v>2330300</v>
       </c>
       <c r="M149" s="1" t="n">
         <v>20366.6666666667</v>
       </c>
       <c r="N149" s="1" t="n">
-        <v>22841.6666666667</v>
+        <v>22883.3333333333</v>
       </c>
       <c r="O149" s="1" t="n">
-        <v>12066.6666666667</v>
+        <v>12108.3333333333</v>
       </c>
     </row>
     <row r="150">
@@ -44511,46 +44834,46 @@
         <v>2015</v>
       </c>
       <c r="B150" s="1" t="n">
-        <v>17905900</v>
+        <v>17857200</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>239600</v>
+        <v>240100</v>
       </c>
       <c r="D150" s="1" t="n">
-        <v>72900</v>
+        <v>72700</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>444300</v>
+        <v>443700</v>
       </c>
       <c r="F150" s="1" t="n">
-        <v>354800</v>
+        <v>354700</v>
       </c>
       <c r="G150" s="1" t="n">
-        <v>4050200</v>
+        <v>4041900</v>
       </c>
       <c r="H150" s="1" t="n">
-        <v>6887000</v>
+        <v>6862700</v>
       </c>
       <c r="I150" s="1" t="n">
-        <v>637400</v>
+        <v>637900</v>
       </c>
       <c r="J150" s="1" t="n">
-        <v>565200</v>
+        <v>565500</v>
       </c>
       <c r="K150" s="1" t="n">
-        <v>2265600</v>
+        <v>2263000</v>
       </c>
       <c r="L150" s="1" t="n">
-        <v>2388900</v>
+        <v>2375000</v>
       </c>
       <c r="M150" s="1" t="n">
-        <v>20250</v>
+        <v>20241.6666666667</v>
       </c>
       <c r="N150" s="1" t="n">
-        <v>23016.6666666667</v>
+        <v>23091.6666666667</v>
       </c>
       <c r="O150" s="1" t="n">
-        <v>12133.3333333333</v>
+        <v>12208.3333333333</v>
       </c>
     </row>
     <row r="151">
@@ -44558,46 +44881,46 @@
         <v>2016</v>
       </c>
       <c r="B151" s="1" t="n">
-        <v>18008700</v>
+        <v>17966900</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>234500</v>
+        <v>235100</v>
       </c>
       <c r="D151" s="1" t="n">
-        <v>72500</v>
+        <v>72100</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>443200</v>
+        <v>441900</v>
       </c>
       <c r="F151" s="1" t="n">
         <v>357600</v>
       </c>
       <c r="G151" s="1" t="n">
-        <v>4073300</v>
+        <v>4063600</v>
       </c>
       <c r="H151" s="1" t="n">
-        <v>6956400</v>
+        <v>6934500</v>
       </c>
       <c r="I151" s="1" t="n">
-        <v>637600</v>
+        <v>638000</v>
       </c>
       <c r="J151" s="1" t="n">
         <v>561100</v>
       </c>
       <c r="K151" s="1" t="n">
-        <v>2204600</v>
+        <v>2198300</v>
       </c>
       <c r="L151" s="1" t="n">
-        <v>2467900</v>
+        <v>2464700</v>
       </c>
       <c r="M151" s="1" t="n">
-        <v>21000</v>
+        <v>20975</v>
       </c>
       <c r="N151" s="1" t="n">
-        <v>23308.3333333333</v>
+        <v>23316.6666666667</v>
       </c>
       <c r="O151" s="1" t="n">
-        <v>12908.3333333333</v>
+        <v>12975</v>
       </c>
     </row>
     <row r="152">
@@ -44605,46 +44928,46 @@
         <v>2017</v>
       </c>
       <c r="B152" s="1" t="n">
-        <v>18395000</v>
+        <v>18372200</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>225700</v>
+        <v>226800</v>
       </c>
       <c r="D152" s="1" t="n">
-        <v>75000</v>
+        <v>74200</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>447100</v>
+        <v>444800</v>
       </c>
       <c r="F152" s="1" t="n">
-        <v>360100</v>
+        <v>359400</v>
       </c>
       <c r="G152" s="1" t="n">
-        <v>4177700</v>
+        <v>4165100</v>
       </c>
       <c r="H152" s="1" t="n">
-        <v>7117300</v>
+        <v>7109200</v>
       </c>
       <c r="I152" s="1" t="n">
-        <v>648100</v>
+        <v>648800</v>
       </c>
       <c r="J152" s="1" t="n">
         <v>562500</v>
       </c>
       <c r="K152" s="1" t="n">
-        <v>2221100</v>
+        <v>2218400</v>
       </c>
       <c r="L152" s="1" t="n">
-        <v>2560300</v>
+        <v>2562900</v>
       </c>
       <c r="M152" s="1" t="n">
-        <v>22200</v>
+        <v>22191.6666666667</v>
       </c>
       <c r="N152" s="1" t="n">
-        <v>22541.6666666667</v>
+        <v>22483.3333333333</v>
       </c>
       <c r="O152" s="1" t="n">
-        <v>12841.6666666667</v>
+        <v>12975</v>
       </c>
     </row>
     <row r="153">
@@ -44652,46 +44975,46 @@
         <v>2018</v>
       </c>
       <c r="B153" s="1" t="n">
-        <v>18723300</v>
+        <v>18706600</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>226700</v>
+        <v>228000</v>
       </c>
       <c r="D153" s="1" t="n">
-        <v>77000</v>
+        <v>76100</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>451800</v>
+        <v>451100</v>
       </c>
       <c r="F153" s="1" t="n">
-        <v>361400</v>
+        <v>359900</v>
       </c>
       <c r="G153" s="1" t="n">
-        <v>4253300</v>
+        <v>4243200</v>
       </c>
       <c r="H153" s="1" t="n">
-        <v>7245900</v>
+        <v>7240400</v>
       </c>
       <c r="I153" s="1" t="n">
-        <v>654000</v>
+        <v>653600</v>
       </c>
       <c r="J153" s="1" t="n">
-        <v>566500</v>
+        <v>565200</v>
       </c>
       <c r="K153" s="1" t="n">
-        <v>2280100</v>
+        <v>2279300</v>
       </c>
       <c r="L153" s="1" t="n">
-        <v>2606400</v>
+        <v>2609900</v>
       </c>
       <c r="M153" s="1" t="n">
-        <v>22383.3333333333</v>
+        <v>22416.6666666667</v>
       </c>
       <c r="N153" s="1" t="n">
-        <v>22658.3333333333</v>
+        <v>22408.3333333333</v>
       </c>
       <c r="O153" s="1" t="n">
-        <v>13000</v>
+        <v>13108.3333333333</v>
       </c>
     </row>
     <row r="154">
@@ -44699,46 +45022,46 @@
         <v>2019</v>
       </c>
       <c r="B154" s="1" t="n">
-        <v>19121200</v>
+        <v>19070800</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>229900</v>
+        <v>231300</v>
       </c>
       <c r="D154" s="1" t="n">
-        <v>79500</v>
+        <v>78100</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>464600</v>
+        <v>463800</v>
       </c>
       <c r="F154" s="1" t="n">
-        <v>363600</v>
+        <v>361700</v>
       </c>
       <c r="G154" s="1" t="n">
-        <v>4330700</v>
+        <v>4300300</v>
       </c>
       <c r="H154" s="1" t="n">
-        <v>7429200</v>
+        <v>7412900</v>
       </c>
       <c r="I154" s="1" t="n">
-        <v>661400</v>
+        <v>661600</v>
       </c>
       <c r="J154" s="1" t="n">
-        <v>576900</v>
+        <v>574500</v>
       </c>
       <c r="K154" s="1" t="n">
-        <v>2307800</v>
+        <v>2305500</v>
       </c>
       <c r="L154" s="1" t="n">
-        <v>2677700</v>
+        <v>2681100</v>
       </c>
       <c r="M154" s="1" t="n">
-        <v>23166.6666666667</v>
+        <v>23191.6666666667</v>
       </c>
       <c r="N154" s="1" t="n">
-        <v>23141.6666666667</v>
+        <v>22783.3333333333</v>
       </c>
       <c r="O154" s="1" t="n">
-        <v>13416.6666666667</v>
+        <v>13483.3333333333</v>
       </c>
     </row>
     <row r="155">
@@ -44746,46 +45069,46 @@
         <v>2020</v>
       </c>
       <c r="B155" s="1" t="n">
-        <v>18043800</v>
+        <v>18068500</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>215500</v>
+        <v>217300</v>
       </c>
       <c r="D155" s="1" t="n">
-        <v>76800</v>
+        <v>76200</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>443300</v>
+        <v>447200</v>
       </c>
       <c r="F155" s="1" t="n">
-        <v>352400</v>
+        <v>351500</v>
       </c>
       <c r="G155" s="1" t="n">
-        <v>4096800</v>
+        <v>4087500</v>
       </c>
       <c r="H155" s="1" t="n">
-        <v>7025900</v>
+        <v>7043400</v>
       </c>
       <c r="I155" s="1" t="n">
-        <v>632600</v>
+        <v>635600</v>
       </c>
       <c r="J155" s="1" t="n">
-        <v>547500</v>
+        <v>545300</v>
       </c>
       <c r="K155" s="1" t="n">
-        <v>2143700</v>
+        <v>2137100</v>
       </c>
       <c r="L155" s="1" t="n">
-        <v>2509200</v>
+        <v>2527300</v>
       </c>
       <c r="M155" s="1" t="n">
-        <v>21958.3333333333</v>
+        <v>22241.6666666667</v>
       </c>
       <c r="N155" s="1" t="n">
-        <v>21841.6666666667</v>
+        <v>21508.3333333333</v>
       </c>
       <c r="O155" s="1" t="n">
-        <v>12366.6666666667</v>
+        <v>12408.3333333333</v>
       </c>
     </row>
     <row r="156">
@@ -44793,46 +45116,46 @@
         <v>2021</v>
       </c>
       <c r="B156" s="1" t="n">
-        <v>18942300</v>
+        <v>18964100</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>222800</v>
+        <v>225100</v>
       </c>
       <c r="D156" s="1" t="n">
-        <v>79900</v>
+        <v>80000</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>468100</v>
+        <v>475500</v>
       </c>
       <c r="F156" s="1" t="n">
-        <v>363500</v>
+        <v>364600</v>
       </c>
       <c r="G156" s="1" t="n">
-        <v>4273400</v>
+        <v>4261800</v>
       </c>
       <c r="H156" s="1" t="n">
-        <v>7393300</v>
+        <v>7404800</v>
       </c>
       <c r="I156" s="1" t="n">
-        <v>656200</v>
+        <v>664000</v>
       </c>
       <c r="J156" s="1" t="n">
-        <v>561700</v>
+        <v>558300</v>
       </c>
       <c r="K156" s="1" t="n">
-        <v>2259600</v>
+        <v>2245900</v>
       </c>
       <c r="L156" s="1" t="n">
-        <v>2663900</v>
+        <v>2683900</v>
       </c>
       <c r="M156" s="1" t="n">
-        <v>22416.6666666667</v>
+        <v>22841.6666666667</v>
       </c>
       <c r="N156" s="1" t="n">
-        <v>23341.6666666667</v>
+        <v>23058.3333333333</v>
       </c>
       <c r="O156" s="1" t="n">
-        <v>13541.6666666667</v>
+        <v>13566.6666666667</v>
       </c>
     </row>
     <row r="157">
@@ -44840,46 +45163,46 @@
         <v>2022</v>
       </c>
       <c r="B157" s="1" t="n">
-        <v>19693000</v>
+        <v>19739500</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>232500</v>
+        <v>234200</v>
       </c>
       <c r="D157" s="1" t="n">
-        <v>84200</v>
+        <v>84100</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>484900</v>
+        <v>492100</v>
       </c>
       <c r="F157" s="1" t="n">
-        <v>373500</v>
+        <v>375600</v>
       </c>
       <c r="G157" s="1" t="n">
-        <v>4403100</v>
+        <v>4392000</v>
       </c>
       <c r="H157" s="1" t="n">
-        <v>7731600</v>
+        <v>7764100</v>
       </c>
       <c r="I157" s="1" t="n">
-        <v>677500</v>
+        <v>687900</v>
       </c>
       <c r="J157" s="1" t="n">
-        <v>581500</v>
+        <v>577800</v>
       </c>
       <c r="K157" s="1" t="n">
-        <v>2376100</v>
+        <v>2356000</v>
       </c>
       <c r="L157" s="1" t="n">
-        <v>2747900</v>
+        <v>2775700</v>
       </c>
       <c r="M157" s="1" t="n">
-        <v>23283.3333333333</v>
+        <v>23850</v>
       </c>
       <c r="N157" s="1" t="n">
-        <v>24733.3333333333</v>
+        <v>24475</v>
       </c>
       <c r="O157" s="1" t="n">
-        <v>14391.6666666667</v>
+        <v>14291.6666666667</v>
       </c>
     </row>
     <row r="158">
@@ -44887,71 +45210,118 @@
         <v>2023</v>
       </c>
       <c r="B158" s="1" t="n">
-        <v>20170900</v>
+        <v>20334800</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>236700</v>
+        <v>238300</v>
       </c>
       <c r="D158" s="1" t="n">
-        <v>89000</v>
+        <v>89300</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>497800</v>
+        <v>505300</v>
       </c>
       <c r="F158" s="1" t="n">
-        <v>386500</v>
+        <v>388600</v>
       </c>
       <c r="G158" s="1" t="n">
-        <v>4506400</v>
+        <v>4522800</v>
       </c>
       <c r="H158" s="1" t="n">
-        <v>7914800</v>
+        <v>8006100</v>
       </c>
       <c r="I158" s="1" t="n">
-        <v>694600</v>
+        <v>706800</v>
       </c>
       <c r="J158" s="1" t="n">
-        <v>592200</v>
+        <v>587000</v>
       </c>
       <c r="K158" s="1" t="n">
-        <v>2461100</v>
+        <v>2442600</v>
       </c>
       <c r="L158" s="1" t="n">
-        <v>2791800</v>
+        <v>2847900</v>
       </c>
       <c r="M158" s="1" t="n">
-        <v>23841.6666666667</v>
+        <v>24808.3333333333</v>
       </c>
       <c r="N158" s="1" t="n">
-        <v>23783.3333333333</v>
+        <v>23641.6666666667</v>
       </c>
       <c r="O158" s="1" t="n">
-        <v>14200</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
         <v>2024</v>
       </c>
-      <c r="B159" s="1"/>
-      <c r="C159" s="1"/>
-      <c r="D159" s="1"/>
-      <c r="E159" s="1"/>
-      <c r="F159" s="1"/>
-      <c r="G159" s="1"/>
-      <c r="H159" s="1"/>
-      <c r="I159" s="1"/>
-      <c r="J159" s="1"/>
-      <c r="K159" s="1"/>
-      <c r="L159" s="1"/>
+      <c r="B159" s="1" t="n">
+        <v>20730500</v>
+      </c>
+      <c r="C159" s="1" t="n">
+        <v>245000</v>
+      </c>
+      <c r="D159" s="1" t="n">
+        <v>92500</v>
+      </c>
+      <c r="E159" s="1" t="n">
+        <v>521300</v>
+      </c>
+      <c r="F159" s="1" t="n">
+        <v>400000</v>
+      </c>
+      <c r="G159" s="1" t="n">
+        <v>4566000</v>
+      </c>
+      <c r="H159" s="1" t="n">
+        <v>8146100</v>
+      </c>
+      <c r="I159" s="1" t="n">
+        <v>724400</v>
+      </c>
+      <c r="J159" s="1" t="n">
+        <v>602200</v>
+      </c>
+      <c r="K159" s="1" t="n">
+        <v>2518900</v>
+      </c>
+      <c r="L159" s="1" t="n">
+        <v>2914000</v>
+      </c>
       <c r="M159" s="1" t="n">
-        <v>25000</v>
+        <v>26383.3333333333</v>
       </c>
       <c r="N159" s="1" t="n">
-        <v>22930</v>
+        <v>22933.3333333333</v>
       </c>
       <c r="O159" s="1" t="n">
-        <v>14410</v>
+        <v>14300</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B160" s="1"/>
+      <c r="C160" s="1"/>
+      <c r="D160" s="1"/>
+      <c r="E160" s="1"/>
+      <c r="F160" s="1"/>
+      <c r="G160" s="1"/>
+      <c r="H160" s="1"/>
+      <c r="I160" s="1"/>
+      <c r="J160" s="1"/>
+      <c r="K160" s="1"/>
+      <c r="L160" s="1"/>
+      <c r="M160" s="1" t="n">
+        <v>27211.1111111111</v>
+      </c>
+      <c r="N160" s="1" t="n">
+        <v>23133.3333333333</v>
+      </c>
+      <c r="O160" s="1" t="n">
+        <v>14400</v>
       </c>
     </row>
   </sheetData>

--- a/FON Macroeconomic Data.xlsx
+++ b/FON Macroeconomic Data.xlsx
@@ -6718,7 +6718,7 @@
         <v>2021</v>
       </c>
       <c r="B156" s="1" t="n">
-        <v>38224832.5</v>
+        <v>38225382.5</v>
       </c>
       <c r="C156" s="1" t="n">
         <v>527056</v>
@@ -6765,46 +6765,46 @@
         <v>2022</v>
       </c>
       <c r="B157" s="1" t="n">
-        <v>38873253</v>
+        <v>38865501</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>531257</v>
+        <v>531061</v>
       </c>
       <c r="D157" s="1" t="n">
-        <v>167200</v>
+        <v>167147</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>1024034</v>
+        <v>1024306</v>
       </c>
       <c r="F157" s="1" t="n">
-        <v>808869</v>
+        <v>808587</v>
       </c>
       <c r="G157" s="1" t="n">
-        <v>8669963</v>
+        <v>8667648</v>
       </c>
       <c r="H157" s="1" t="n">
-        <v>15155836</v>
+        <v>15155192</v>
       </c>
       <c r="I157" s="1" t="n">
-        <v>1413498</v>
+        <v>1413346</v>
       </c>
       <c r="J157" s="1" t="n">
-        <v>1178796</v>
+        <v>1178761</v>
       </c>
       <c r="K157" s="1" t="n">
-        <v>4512731</v>
+        <v>4513589</v>
       </c>
       <c r="L157" s="1" t="n">
-        <v>5358845</v>
+        <v>5356870</v>
       </c>
       <c r="M157" s="1" t="n">
-        <v>43869</v>
+        <v>43891</v>
       </c>
       <c r="N157" s="1" t="n">
-        <v>44631</v>
+        <v>44626</v>
       </c>
       <c r="O157" s="1" t="n">
-        <v>40603</v>
+        <v>40604</v>
       </c>
     </row>
     <row r="158">
@@ -6812,46 +6812,46 @@
         <v>2023</v>
       </c>
       <c r="B158" s="1" t="n">
-        <v>39936359</v>
+        <v>39905784.25</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>538789</v>
+        <v>538041</v>
       </c>
       <c r="D158" s="1" t="n">
-        <v>173734</v>
+        <v>173270</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>1053005</v>
+        <v>1052601</v>
       </c>
       <c r="F158" s="1" t="n">
-        <v>831103</v>
+        <v>829937</v>
       </c>
       <c r="G158" s="1" t="n">
-        <v>8821696</v>
+        <v>8818050</v>
       </c>
       <c r="H158" s="1" t="n">
-        <v>15632481</v>
+        <v>15618269</v>
       </c>
       <c r="I158" s="1" t="n">
-        <v>1453202</v>
+        <v>1452054</v>
       </c>
       <c r="J158" s="1" t="n">
-        <v>1210257</v>
+        <v>1209273</v>
       </c>
       <c r="K158" s="1" t="n">
-        <v>4688576</v>
+        <v>4688032</v>
       </c>
       <c r="L158" s="1" t="n">
-        <v>5515296</v>
+        <v>5512217</v>
       </c>
       <c r="M158" s="1" t="n">
-        <v>45419</v>
+        <v>45410</v>
       </c>
       <c r="N158" s="1" t="n">
-        <v>44614</v>
+        <v>44611</v>
       </c>
       <c r="O158" s="1" t="n">
-        <v>40916</v>
+        <v>40939</v>
       </c>
     </row>
     <row r="159">
@@ -6859,91 +6859,140 @@
         <v>2024</v>
       </c>
       <c r="B159" s="1" t="n">
-        <v>41117821</v>
+        <v>41029607</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>546869</v>
+        <v>545080</v>
       </c>
       <c r="D159" s="1" t="n">
-        <v>179709</v>
+        <v>178869</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>1082769</v>
+        <v>1080310</v>
       </c>
       <c r="F159" s="1" t="n">
-        <v>858293</v>
+        <v>857114</v>
       </c>
       <c r="G159" s="1" t="n">
-        <v>8995474</v>
+        <v>8982312</v>
       </c>
       <c r="H159" s="1" t="n">
-        <v>16144797</v>
+        <v>16090358</v>
       </c>
       <c r="I159" s="1" t="n">
-        <v>1492144</v>
+        <v>1487953</v>
       </c>
       <c r="J159" s="1" t="n">
-        <v>1247868</v>
+        <v>1245196</v>
       </c>
       <c r="K159" s="1" t="n">
-        <v>4909030</v>
+        <v>4901795</v>
       </c>
       <c r="L159" s="1" t="n">
-        <v>5671114</v>
+        <v>5659205</v>
       </c>
       <c r="M159" s="1" t="n">
-        <v>47595</v>
+        <v>47683</v>
       </c>
       <c r="N159" s="1" t="n">
-        <v>45257</v>
+        <v>45274</v>
       </c>
       <c r="O159" s="1" t="n">
-        <v>41410</v>
+        <v>41444</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="B160" s="1"/>
+      <c r="B160" s="1" t="n">
+        <v>41566056.25</v>
+      </c>
       <c r="C160" s="1" t="n">
-        <v>549911</v>
+        <v>550202</v>
       </c>
       <c r="D160" s="1" t="n">
-        <v>182657</v>
+        <v>181594</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>1093245</v>
+        <v>1095157</v>
       </c>
       <c r="F160" s="1" t="n">
-        <v>869682</v>
+        <v>874711</v>
       </c>
       <c r="G160" s="1" t="n">
-        <v>9058297</v>
+        <v>9051022</v>
       </c>
       <c r="H160" s="1" t="n">
-        <v>16258260</v>
+        <v>16216961</v>
       </c>
       <c r="I160" s="1" t="n">
-        <v>1509702</v>
+        <v>1508582</v>
       </c>
       <c r="J160" s="1" t="n">
-        <v>1266959</v>
+        <v>1266289</v>
       </c>
       <c r="K160" s="1" t="n">
-        <v>5029346</v>
+        <v>5024631</v>
       </c>
       <c r="L160" s="1" t="n">
-        <v>5697536</v>
+        <v>5702544</v>
       </c>
       <c r="M160" s="1" t="n">
-        <v>48278</v>
+        <v>49150</v>
       </c>
       <c r="N160" s="1" t="n">
-        <v>45950</v>
+        <v>46031</v>
       </c>
       <c r="O160" s="1" t="n">
-        <v>41830</v>
+        <v>42108</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B161" s="1" t="n">
+        <v>41744389.6666667</v>
+      </c>
+      <c r="C161" s="1" t="n">
+        <v>552462</v>
+      </c>
+      <c r="D161" s="1" t="n">
+        <v>182989</v>
+      </c>
+      <c r="E161" s="1" t="n">
+        <v>1103419</v>
+      </c>
+      <c r="F161" s="1" t="n">
+        <v>883522</v>
+      </c>
+      <c r="G161" s="1" t="n">
+        <v>9067114</v>
+      </c>
+      <c r="H161" s="1" t="n">
+        <v>16262121</v>
+      </c>
+      <c r="I161" s="1" t="n">
+        <v>1517379</v>
+      </c>
+      <c r="J161" s="1" t="n">
+        <v>1278402</v>
+      </c>
+      <c r="K161" s="1" t="n">
+        <v>5101050</v>
+      </c>
+      <c r="L161" s="1" t="n">
+        <v>5710598</v>
+      </c>
+      <c r="M161" s="1" t="n">
+        <v>50356</v>
+      </c>
+      <c r="N161" s="1" t="n">
+        <v>45904</v>
+      </c>
+      <c r="O161" s="1" t="n">
+        <v>43091</v>
       </c>
     </row>
   </sheetData>
@@ -12277,20 +12326,61 @@
       <c r="A160" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="B160" s="4"/>
-      <c r="C160" s="4"/>
-      <c r="D160" s="4"/>
-      <c r="E160" s="4"/>
-      <c r="F160" s="4"/>
-      <c r="G160" s="4"/>
-      <c r="H160" s="4"/>
-      <c r="I160" s="4"/>
-      <c r="J160" s="4"/>
-      <c r="K160" s="4"/>
-      <c r="L160" s="4"/>
+      <c r="B160" s="4" t="n">
+        <v>119.85401459854</v>
+      </c>
+      <c r="C160" s="4" t="n">
+        <v>117.621776504298</v>
+      </c>
+      <c r="D160" s="4" t="n">
+        <v>121.537345902828</v>
+      </c>
+      <c r="E160" s="4" t="n">
+        <v>121.537345902828</v>
+      </c>
+      <c r="F160" s="4" t="n">
+        <v>119.838945827233</v>
+      </c>
+      <c r="G160" s="4" t="n">
+        <v>121.234939759036</v>
+      </c>
+      <c r="H160" s="4" t="n">
+        <v>119.653179190751</v>
+      </c>
+      <c r="I160" s="4" t="n">
+        <v>119.709090909091</v>
+      </c>
+      <c r="J160" s="4" t="n">
+        <v>117.768301350391</v>
+      </c>
+      <c r="K160" s="4" t="n">
+        <v>119.004837595024</v>
+      </c>
+      <c r="L160" s="4" t="n">
+        <v>119.712990936556</v>
+      </c>
       <c r="M160" s="4"/>
       <c r="N160" s="4"/>
       <c r="O160" s="4"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B161" s="4"/>
+      <c r="C161" s="4"/>
+      <c r="D161" s="4"/>
+      <c r="E161" s="4"/>
+      <c r="F161" s="4"/>
+      <c r="G161" s="4"/>
+      <c r="H161" s="4"/>
+      <c r="I161" s="4"/>
+      <c r="J161" s="4"/>
+      <c r="K161" s="4"/>
+      <c r="L161" s="4"/>
+      <c r="M161" s="4"/>
+      <c r="N161" s="4"/>
+      <c r="O161" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -17675,7 +17765,7 @@
         <v>2022</v>
       </c>
       <c r="B157" s="1" t="n">
-        <v>2850940</v>
+        <v>2864159</v>
       </c>
       <c r="C157" s="1" t="n">
         <v>42036</v>
@@ -17722,7 +17812,7 @@
         <v>2023</v>
       </c>
       <c r="B158" s="1" t="n">
-        <v>2933810</v>
+        <v>2965201</v>
       </c>
       <c r="C158" s="1" t="n">
         <v>40363</v>
@@ -17769,7 +17859,7 @@
         <v>2024</v>
       </c>
       <c r="B159" s="1" t="n">
-        <v>3072346</v>
+        <v>3108551</v>
       </c>
       <c r="C159" s="1" t="n">
         <v>42219</v>
@@ -17815,7 +17905,9 @@
       <c r="A160" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="B160" s="1"/>
+      <c r="B160" s="1" t="n">
+        <v>3245257</v>
+      </c>
       <c r="C160" s="1"/>
       <c r="D160" s="1"/>
       <c r="E160" s="1"/>
@@ -17829,6 +17921,27 @@
       <c r="M160" s="1"/>
       <c r="N160" s="1"/>
       <c r="O160" s="1"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B161" s="1" t="n">
+        <v>3383106</v>
+      </c>
+      <c r="C161" s="1"/>
+      <c r="D161" s="1"/>
+      <c r="E161" s="1"/>
+      <c r="F161" s="1"/>
+      <c r="G161" s="1"/>
+      <c r="H161" s="1"/>
+      <c r="I161" s="1"/>
+      <c r="J161" s="1"/>
+      <c r="K161" s="1"/>
+      <c r="L161" s="1"/>
+      <c r="M161" s="1"/>
+      <c r="N161" s="1"/>
+      <c r="O161" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -23213,7 +23326,7 @@
         <v>2022</v>
       </c>
       <c r="B157" s="1" t="n">
-        <v>2583192.98941799</v>
+        <v>2595170.52248677</v>
       </c>
       <c r="C157" s="1" t="n">
         <v>38088.1746031746</v>
@@ -23260,7 +23373,7 @@
         <v>2023</v>
       </c>
       <c r="B158" s="1" t="n">
-        <v>2558446.6581795</v>
+        <v>2585821.36855506</v>
       </c>
       <c r="C158" s="1" t="n">
         <v>35198.7969446213</v>
@@ -23307,7 +23420,7 @@
         <v>2024</v>
       </c>
       <c r="B159" s="1" t="n">
-        <v>2615981.36730889</v>
+        <v>2646808.49596022</v>
       </c>
       <c r="C159" s="1" t="n">
         <v>35947.81230578</v>
@@ -23353,7 +23466,9 @@
       <c r="A160" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="B160" s="1"/>
+      <c r="B160" s="1" t="n">
+        <v>2707674.84165652</v>
+      </c>
       <c r="C160" s="1"/>
       <c r="D160" s="1"/>
       <c r="E160" s="1"/>
@@ -23367,6 +23482,25 @@
       <c r="M160" s="1"/>
       <c r="N160" s="1"/>
       <c r="O160" s="1"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B161" s="1"/>
+      <c r="C161" s="1"/>
+      <c r="D161" s="1"/>
+      <c r="E161" s="1"/>
+      <c r="F161" s="1"/>
+      <c r="G161" s="1"/>
+      <c r="H161" s="1"/>
+      <c r="I161" s="1"/>
+      <c r="J161" s="1"/>
+      <c r="K161" s="1"/>
+      <c r="L161" s="1"/>
+      <c r="M161" s="1"/>
+      <c r="N161" s="1"/>
+      <c r="O161" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -28704,7 +28838,7 @@
         <v>2021</v>
       </c>
       <c r="B156" s="1" t="n">
-        <v>66339.5451111525</v>
+        <v>66338.590594875</v>
       </c>
       <c r="C156" s="1" t="n">
         <v>73384.9913481679</v>
@@ -28751,46 +28885,46 @@
         <v>2022</v>
       </c>
       <c r="B157" s="1" t="n">
-        <v>73339.3729616608</v>
+        <v>73694.1227130972</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>79125.5456398692</v>
+        <v>79154.748701185</v>
       </c>
       <c r="D157" s="1" t="n">
-        <v>56812.2009569378</v>
+        <v>56830.2153194493</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>54908.3331217518</v>
+        <v>54893.7524528803</v>
       </c>
       <c r="F157" s="1" t="n">
-        <v>55525.6784473135</v>
+        <v>55545.0433905071</v>
       </c>
       <c r="G157" s="1" t="n">
-        <v>64145.4871260696</v>
+        <v>64162.6194326304</v>
       </c>
       <c r="H157" s="1" t="n">
-        <v>70287.1158014642</v>
+        <v>70290.1025602315</v>
       </c>
       <c r="I157" s="1" t="n">
-        <v>62442.2531903123</v>
+        <v>62448.9686177341</v>
       </c>
       <c r="J157" s="1" t="n">
-        <v>99496.4353458953</v>
+        <v>99499.3896133313</v>
       </c>
       <c r="K157" s="1" t="n">
-        <v>104148.685131022</v>
+        <v>104128.88723364</v>
       </c>
       <c r="L157" s="1" t="n">
-        <v>74671.687649111</v>
+        <v>74699.2180135042</v>
       </c>
       <c r="M157" s="1" t="n">
-        <v>88285.5775148738</v>
+        <v>88241.3251008179</v>
       </c>
       <c r="N157" s="1" t="n">
-        <v>119647.778449956</v>
+        <v>119661.184063102</v>
       </c>
       <c r="O157" s="1" t="n">
-        <v>108415.634312736</v>
+        <v>108412.964239976</v>
       </c>
     </row>
     <row r="158">
@@ -28798,46 +28932,46 @@
         <v>2023</v>
       </c>
       <c r="B158" s="1" t="n">
-        <v>73462.1300855193</v>
+        <v>74305.0426330113</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>74914.2985472977</v>
+        <v>75018.4465496124</v>
       </c>
       <c r="D158" s="1" t="n">
-        <v>58330.551302566</v>
+        <v>58486.7547757835</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>57442.2723538825</v>
+        <v>57464.3193384768</v>
       </c>
       <c r="F158" s="1" t="n">
-        <v>55905.2247435035</v>
+        <v>55983.767442589</v>
       </c>
       <c r="G158" s="1" t="n">
-        <v>66029.8201162225</v>
+        <v>66057.1214724344</v>
       </c>
       <c r="H158" s="1" t="n">
-        <v>72835.0157598145</v>
+        <v>72901.292710479</v>
       </c>
       <c r="I158" s="1" t="n">
-        <v>64027.5749689307</v>
+        <v>64078.1954390126</v>
       </c>
       <c r="J158" s="1" t="n">
-        <v>93281.8401380864</v>
+        <v>93357.7446945396</v>
       </c>
       <c r="K158" s="1" t="n">
-        <v>96192.9592268527</v>
+        <v>96204.1214735736</v>
       </c>
       <c r="L158" s="1" t="n">
-        <v>75148.2785330107</v>
+        <v>75190.2546652282</v>
       </c>
       <c r="M158" s="1" t="n">
-        <v>92076.0034346859</v>
+        <v>92094.25236732</v>
       </c>
       <c r="N158" s="1" t="n">
-        <v>119827.856726588</v>
+        <v>119835.914908879</v>
       </c>
       <c r="O158" s="1" t="n">
-        <v>119733.111741128</v>
+        <v>119665.844304941</v>
       </c>
     </row>
     <row r="159">
@@ -28845,53 +28979,55 @@
         <v>2024</v>
       </c>
       <c r="B159" s="1" t="n">
-        <v>74720.5451378369</v>
+        <v>75763.6065098064</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>77201.3041514513</v>
+        <v>77454.6855507448</v>
       </c>
       <c r="D159" s="1" t="n">
-        <v>60592.4021612718</v>
+        <v>60876.9546427833</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>60343.4342874611</v>
+        <v>60480.7879219854</v>
       </c>
       <c r="F159" s="1" t="n">
-        <v>56276.8192214081</v>
+        <v>56354.2305924299</v>
       </c>
       <c r="G159" s="1" t="n">
-        <v>68564.5914823388</v>
+        <v>68665.0608440232</v>
       </c>
       <c r="H159" s="1" t="n">
-        <v>74142.7718168274</v>
+        <v>74393.6213227823</v>
       </c>
       <c r="I159" s="1" t="n">
-        <v>64420.726149755</v>
+        <v>64602.1749342889</v>
       </c>
       <c r="J159" s="1" t="n">
-        <v>90425.4296127475</v>
+        <v>90619.4687422703</v>
       </c>
       <c r="K159" s="1" t="n">
-        <v>96543.9200819714</v>
+        <v>96686.4179346546</v>
       </c>
       <c r="L159" s="1" t="n">
-        <v>75662.2067551455</v>
+        <v>75821.4272145999</v>
       </c>
       <c r="M159" s="1" t="n">
-        <v>91375.1444479462</v>
+        <v>91206.5096575299</v>
       </c>
       <c r="N159" s="1" t="n">
-        <v>113197.958326889</v>
+        <v>113155.453461148</v>
       </c>
       <c r="O159" s="1" t="n">
-        <v>136875.150929727</v>
+        <v>136762.860727729</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="B160" s="1"/>
+      <c r="B160" s="1" t="n">
+        <v>78074.6910527505</v>
+      </c>
       <c r="C160" s="1"/>
       <c r="D160" s="1"/>
       <c r="E160" s="1"/>
@@ -28905,6 +29041,27 @@
       <c r="M160" s="1"/>
       <c r="N160" s="1"/>
       <c r="O160" s="1"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B161" s="1" t="n">
+        <v>81043.3695884514</v>
+      </c>
+      <c r="C161" s="1"/>
+      <c r="D161" s="1"/>
+      <c r="E161" s="1"/>
+      <c r="F161" s="1"/>
+      <c r="G161" s="1"/>
+      <c r="H161" s="1"/>
+      <c r="I161" s="1"/>
+      <c r="J161" s="1"/>
+      <c r="K161" s="1"/>
+      <c r="L161" s="1"/>
+      <c r="M161" s="1"/>
+      <c r="N161" s="1"/>
+      <c r="O161" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -34242,7 +34399,7 @@
         <v>2021</v>
       </c>
       <c r="B156" s="1" t="n">
-        <v>64184.4468942648</v>
+        <v>64183.5233862844</v>
       </c>
       <c r="C156" s="1" t="n">
         <v>71001.0156405297</v>
@@ -34289,46 +34446,46 @@
         <v>2022</v>
       </c>
       <c r="B157" s="1" t="n">
-        <v>66451.6805274308</v>
+        <v>66773.1138339571</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>71694.4428086117</v>
+        <v>71720.9032543806</v>
       </c>
       <c r="D157" s="1" t="n">
-        <v>51476.6635654794</v>
+        <v>51492.9861029402</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>49751.5981328042</v>
+        <v>49738.3868124643</v>
       </c>
       <c r="F157" s="1" t="n">
-        <v>50310.9652598012</v>
+        <v>50328.511537695</v>
       </c>
       <c r="G157" s="1" t="n">
-        <v>58121.2416420075</v>
+        <v>58136.7649621056</v>
       </c>
       <c r="H157" s="1" t="n">
-        <v>63686.0771481521</v>
+        <v>63688.7834044426</v>
       </c>
       <c r="I157" s="1" t="n">
-        <v>56577.9675070951</v>
+        <v>56584.0522528411</v>
       </c>
       <c r="J157" s="1" t="n">
-        <v>90152.1934020348</v>
+        <v>90154.8702184285</v>
       </c>
       <c r="K157" s="1" t="n">
-        <v>94367.5255486108</v>
+        <v>94349.5869775711</v>
       </c>
       <c r="L157" s="1" t="n">
-        <v>67658.8704228056</v>
+        <v>67683.8152635587</v>
       </c>
       <c r="M157" s="1" t="n">
-        <v>79994.2071397997</v>
+        <v>79954.110706429</v>
       </c>
       <c r="N157" s="1" t="n">
-        <v>108411.016188122</v>
+        <v>108423.162808499</v>
       </c>
       <c r="O157" s="1" t="n">
-        <v>98233.7427304548</v>
+        <v>98231.3234184971</v>
       </c>
     </row>
     <row r="158">
@@ -34336,46 +34493,46 @@
         <v>2023</v>
       </c>
       <c r="B158" s="1" t="n">
-        <v>64063.0924361308</v>
+        <v>64798.1593935235</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>65329.4646784201</v>
+        <v>65420.2875703176</v>
       </c>
       <c r="D158" s="1" t="n">
-        <v>50867.5081378201</v>
+        <v>51003.7263162466</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>50092.8791373768</v>
+        <v>50112.105342911</v>
       </c>
       <c r="F158" s="1" t="n">
-        <v>48752.4875229789</v>
+        <v>48820.9811561725</v>
       </c>
       <c r="G158" s="1" t="n">
-        <v>57581.7018200031</v>
+        <v>57605.5101319129</v>
       </c>
       <c r="H158" s="1" t="n">
-        <v>63516.2136161336</v>
+        <v>63574.0108296348</v>
       </c>
       <c r="I158" s="1" t="n">
-        <v>55835.6318952483</v>
+        <v>55879.7757806794</v>
       </c>
       <c r="J158" s="1" t="n">
-        <v>81346.9898085158</v>
+        <v>81413.1828335578</v>
       </c>
       <c r="K158" s="1" t="n">
-        <v>83885.6487210619</v>
+        <v>83895.3828254588</v>
       </c>
       <c r="L158" s="1" t="n">
-        <v>65533.5083324155</v>
+        <v>65570.1138710137</v>
       </c>
       <c r="M158" s="1" t="n">
-        <v>80295.4326578738</v>
+        <v>80311.3467493497</v>
       </c>
       <c r="N158" s="1" t="n">
-        <v>104496.603256159</v>
+        <v>104503.630442498</v>
       </c>
       <c r="O158" s="1" t="n">
-        <v>104413.980321671</v>
+        <v>104355.319349312</v>
       </c>
     </row>
     <row r="159">
@@ -34383,53 +34540,55 @@
         <v>2024</v>
       </c>
       <c r="B159" s="1" t="n">
-        <v>63621.5953007064</v>
+        <v>64509.7208939931</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>65733.863696388</v>
+        <v>65949.6079580612</v>
       </c>
       <c r="D159" s="1" t="n">
-        <v>51592.0391304801</v>
+        <v>51834.3243384792</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>51380.0528115735</v>
+        <v>51497.0040106401</v>
       </c>
       <c r="F159" s="1" t="n">
-        <v>47917.4905738527</v>
+        <v>47983.4033011989</v>
       </c>
       <c r="G159" s="1" t="n">
-        <v>58380.0437108789</v>
+        <v>58465.589407279</v>
       </c>
       <c r="H159" s="1" t="n">
-        <v>63129.6441199836</v>
+        <v>63343.2325744013</v>
       </c>
       <c r="I159" s="1" t="n">
-        <v>54851.7059199281</v>
+        <v>55006.2023989906</v>
       </c>
       <c r="J159" s="1" t="n">
-        <v>76993.684629872</v>
+        <v>77158.9012908081</v>
       </c>
       <c r="K159" s="1" t="n">
-        <v>82203.3377950906</v>
+        <v>82324.6690929004</v>
       </c>
       <c r="L159" s="1" t="n">
-        <v>64423.3830046919</v>
+        <v>64558.9529422013</v>
       </c>
       <c r="M159" s="1" t="n">
-        <v>77802.3293310667</v>
+        <v>77658.7434622847</v>
       </c>
       <c r="N159" s="1" t="n">
-        <v>96383.5941005826</v>
+        <v>96347.4028848803</v>
       </c>
       <c r="O159" s="1" t="n">
-        <v>116543.7891695</v>
+        <v>116448.178494089</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="B160" s="1"/>
+      <c r="B160" s="1" t="n">
+        <v>65141.4900988235</v>
+      </c>
       <c r="C160" s="1"/>
       <c r="D160" s="1"/>
       <c r="E160" s="1"/>
@@ -34443,6 +34602,25 @@
       <c r="M160" s="1"/>
       <c r="N160" s="1"/>
       <c r="O160" s="1"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B161" s="1"/>
+      <c r="C161" s="1"/>
+      <c r="D161" s="1"/>
+      <c r="E161" s="1"/>
+      <c r="F161" s="1"/>
+      <c r="G161" s="1"/>
+      <c r="H161" s="1"/>
+      <c r="I161" s="1"/>
+      <c r="J161" s="1"/>
+      <c r="K161" s="1"/>
+      <c r="L161" s="1"/>
+      <c r="M161" s="1"/>
+      <c r="N161" s="1"/>
+      <c r="O161" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -39681,7 +39859,7 @@
         <v>2022</v>
       </c>
       <c r="B157" s="1" t="n">
-        <v>130864.155090959</v>
+        <v>131470.935053409</v>
       </c>
       <c r="C157" s="1" t="n">
         <v>162630.976102368</v>
@@ -39728,7 +39906,7 @@
         <v>2023</v>
       </c>
       <c r="B158" s="1" t="n">
-        <v>125816.170219501</v>
+        <v>127162.370348125</v>
       </c>
       <c r="C158" s="1" t="n">
         <v>147707.918357622</v>
@@ -39761,10 +39939,10 @@
         <v>126913.408606952</v>
       </c>
       <c r="M158" s="1" t="n">
-        <v>147004.565235659</v>
+        <v>146708.880558685</v>
       </c>
       <c r="N158" s="1" t="n">
-        <v>197194.703884538</v>
+        <v>197473.129163584</v>
       </c>
       <c r="O158" s="1" t="n">
         <v>305157.315631536</v>
@@ -39775,7 +39953,7 @@
         <v>2024</v>
       </c>
       <c r="B159" s="1" t="n">
-        <v>126189.979368992</v>
+        <v>127677.021584632</v>
       </c>
       <c r="C159" s="1" t="n">
         <v>146725.764513388</v>
@@ -39821,7 +39999,9 @@
       <c r="A160" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="B160" s="1"/>
+      <c r="B160" s="1" t="n">
+        <v>128760.923958995</v>
+      </c>
       <c r="C160" s="1"/>
       <c r="D160" s="1"/>
       <c r="E160" s="1"/>
@@ -39835,6 +40015,25 @@
       <c r="M160" s="1"/>
       <c r="N160" s="1"/>
       <c r="O160" s="1"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B161" s="1"/>
+      <c r="C161" s="1"/>
+      <c r="D161" s="1"/>
+      <c r="E161" s="1"/>
+      <c r="F161" s="1"/>
+      <c r="G161" s="1"/>
+      <c r="H161" s="1"/>
+      <c r="I161" s="1"/>
+      <c r="J161" s="1"/>
+      <c r="K161" s="1"/>
+      <c r="L161" s="1"/>
+      <c r="M161" s="1"/>
+      <c r="N161" s="1"/>
+      <c r="O161" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -45243,10 +45442,10 @@
         <v>2847900</v>
       </c>
       <c r="M158" s="1" t="n">
-        <v>24808.3333333333</v>
+        <v>24858.3333333333</v>
       </c>
       <c r="N158" s="1" t="n">
-        <v>23641.6666666667</v>
+        <v>23608.3333333333</v>
       </c>
       <c r="O158" s="1" t="n">
         <v>14000</v>
@@ -45303,25 +45502,72 @@
       <c r="A160" s="2" t="n">
         <v>2025</v>
       </c>
-      <c r="B160" s="1"/>
-      <c r="C160" s="1"/>
-      <c r="D160" s="1"/>
-      <c r="E160" s="1"/>
-      <c r="F160" s="1"/>
-      <c r="G160" s="1"/>
-      <c r="H160" s="1"/>
-      <c r="I160" s="1"/>
-      <c r="J160" s="1"/>
-      <c r="K160" s="1"/>
-      <c r="L160" s="1"/>
+      <c r="B160" s="1" t="n">
+        <v>21028700</v>
+      </c>
+      <c r="C160" s="1" t="n">
+        <v>244800</v>
+      </c>
+      <c r="D160" s="1" t="n">
+        <v>93500</v>
+      </c>
+      <c r="E160" s="1" t="n">
+        <v>523500</v>
+      </c>
+      <c r="F160" s="1" t="n">
+        <v>405200</v>
+      </c>
+      <c r="G160" s="1" t="n">
+        <v>4644800</v>
+      </c>
+      <c r="H160" s="1" t="n">
+        <v>8227000</v>
+      </c>
+      <c r="I160" s="1" t="n">
+        <v>736200</v>
+      </c>
+      <c r="J160" s="1" t="n">
+        <v>617400</v>
+      </c>
+      <c r="K160" s="1" t="n">
+        <v>2590100</v>
+      </c>
+      <c r="L160" s="1" t="n">
+        <v>2946200</v>
+      </c>
       <c r="M160" s="1" t="n">
-        <v>27211.1111111111</v>
+        <v>27116.6666666667</v>
       </c>
       <c r="N160" s="1" t="n">
-        <v>23133.3333333333</v>
+        <v>22975</v>
       </c>
       <c r="O160" s="1" t="n">
-        <v>14400</v>
+        <v>14516.6666666667</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B161" s="1"/>
+      <c r="C161" s="1"/>
+      <c r="D161" s="1"/>
+      <c r="E161" s="1"/>
+      <c r="F161" s="1"/>
+      <c r="G161" s="1"/>
+      <c r="H161" s="1"/>
+      <c r="I161" s="1"/>
+      <c r="J161" s="1"/>
+      <c r="K161" s="1"/>
+      <c r="L161" s="1"/>
+      <c r="M161" s="1" t="n">
+        <v>26911.1111111111</v>
+      </c>
+      <c r="N161" s="1" t="n">
+        <v>23588.8888888889</v>
+      </c>
+      <c r="O161" s="1" t="n">
+        <v>15233.3333333333</v>
       </c>
     </row>
   </sheetData>
